--- a/outputs/019fcf4b-cafe-75c0-814f-d0b3e093c2ac/trend-meme-stock-cases.xlsx
+++ b/outputs/019fcf4b-cafe-75c0-814f-d0b3e093c2ac/trend-meme-stock-cases.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_안내" sheetId="1" r:id="Rb4ebd207e3114429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_유행이벤트" sheetId="2" r:id="Raf14ee8c128a4edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_종목반응" sheetId="3" r:id="Rded66f7fccea48f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_출처" sheetId="4" r:id="R67ceea24a0454ddf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_판정기준" sheetId="5" r:id="Rbf1f818408064f5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_안내" sheetId="1" r:id="R2a1c0cdb9f8c45b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_유행이벤트" sheetId="2" r:id="R5de175dda10947f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_종목반응" sheetId="3" r:id="R3c950a999df740f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_출처" sheetId="4" r:id="R19a806caaa15442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_판정기준" sheetId="5" r:id="Rd7a186bd37664a64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,12 +17,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="202" formatCode="@"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="33">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -169,8 +171,54 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF17213C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="22"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF5C667A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF5C667A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF157A5A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FFA65D00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFA65D00"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="22">
+  <x:fills count="48">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -277,8 +325,138 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF071A52"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4006D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163D8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6C3BE8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF23A8E0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF157A5A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA65D00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF071A52"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4006D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163D8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6C3BE8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF23A8E0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF157A5A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA65D00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="20">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -362,11 +540,93 @@
         <x:color rgb="FFD7DEEC"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEEC"/>
+      </x:right>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="184">
+  <x:cellXfs count="781">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -810,6 +1070,1271 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="29" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="29" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="26" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="26" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="25" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="13" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="41" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="26" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="39" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="39" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="25" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="13" fillId="45" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="47" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -911,6 +2436,620 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="975"/>
+              <a:t>연도별 유행·트렌드 사건 수</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="975"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>사건 수</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="F4006D"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'00_안내'!$A$49:$A$66</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'00_안내'!$B$49:$B$66</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="600"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="30"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="975"/>
+              <a:t>대분류별 사건 수</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="975"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>전체 사건</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="163D8C"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'00_안내'!$D$49:$D$57</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'00_안내'!$E$49:$E$57</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="975"/>
+              <a:t>주가 연결 상태 — 70건 확인, 228건 조사 후보</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="975"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:doughnutChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>사건 수</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'00_안내'!$I$49:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'00_안내'!$J$49:$J$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="975"/>
+              <a:t>대분류별 주가 연결률 — 표본 크기 유의</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="975"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>주가 연결률</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="6C3BE8"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'00_안내'!$K$49:$K$57</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'00_안내'!$L$49:$L$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c1b4ec7a44d43d7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb476cb21c70844bd"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26224abf435c4ec9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ec5a1962078468f"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1142,405 +3281,1601 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="94" t="str">
-        <x:v>키움 트렌드 인사이트 — 2009~2026 비정치 유행·밈·트렌드 원장</x:v>
-      </x:c>
-      <x:c r="B1"/>
-      <x:c r="C1"/>
-      <x:c r="D1"/>
-      <x:c r="E1"/>
-      <x:c r="F1"/>
-      <x:c r="G1"/>
-      <x:c r="H1"/>
-      <x:c r="I1"/>
-      <x:c r="J1"/>
-    </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="98" t="str">
-        <x:v>최신 연도부터 확인하고, 같은 연도 안에서는 표준 대분류·소분류로 탐색합니다. 주가 연결 여부와 무관하게 유행 사실을 먼저 축적하며 정치 테마는 제외합니다.</x:v>
-      </x:c>
-      <x:c r="B2" s="98"/>
-      <x:c r="C2" s="98"/>
-      <x:c r="D2" s="98"/>
-      <x:c r="E2" s="98"/>
-      <x:c r="F2" s="98"/>
-      <x:c r="G2" s="98"/>
-      <x:c r="H2" s="98"/>
-      <x:c r="I2" s="98"/>
-      <x:c r="J2" s="98"/>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="484" t="str">
+        <x:v>키움 트렌드 인사이트 — 데이터 한눈에 보기</x:v>
+      </x:c>
+      <x:c r="B1" s="484"/>
+      <x:c r="C1" s="484"/>
+      <x:c r="D1" s="484"/>
+      <x:c r="E1" s="484"/>
+      <x:c r="F1" s="484"/>
+      <x:c r="G1" s="484"/>
+      <x:c r="H1" s="484"/>
+      <x:c r="I1" s="484"/>
+      <x:c r="J1" s="484"/>
+      <x:c r="K1" s="484"/>
+      <x:c r="L1" s="484"/>
+      <x:c r="M1" s="484"/>
+      <x:c r="N1" s="484"/>
+      <x:c r="O1" s="484"/>
+      <x:c r="P1" s="484"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="488" t="str">
+        <x:v>2009~2026년 비정치 인터넷·SNS 유행 298건을 연도·카테고리·주가 연결 상태로 요약했습니다. 유행은 매수 신호가 아니라 기업 조사의 출발점입니다.</x:v>
+      </x:c>
+      <x:c r="B2" s="488"/>
+      <x:c r="C2" s="488"/>
+      <x:c r="D2" s="488"/>
+      <x:c r="E2" s="488"/>
+      <x:c r="F2" s="488"/>
+      <x:c r="G2" s="488"/>
+      <x:c r="H2" s="488"/>
+      <x:c r="I2" s="488"/>
+      <x:c r="J2" s="488"/>
+      <x:c r="K2" s="488"/>
+      <x:c r="L2" s="488"/>
+      <x:c r="M2" s="488"/>
+      <x:c r="N2" s="488"/>
+      <x:c r="O2" s="488"/>
+      <x:c r="P2" s="488"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="194" t="str">
+        <x:v>읽는 순서  ① 핵심 숫자 → ② 데이터가 말하는 세 가지 → ③ 연도·카테고리 분포 → ④ 주가 연결 정도</x:v>
+      </x:c>
+      <x:c r="B3" s="194"/>
+      <x:c r="C3" s="194"/>
+      <x:c r="D3" s="194"/>
+      <x:c r="E3" s="194"/>
+      <x:c r="F3" s="194"/>
+      <x:c r="G3" s="194"/>
+      <x:c r="H3" s="194"/>
+      <x:c r="I3" s="194"/>
+      <x:c r="J3" s="194"/>
+      <x:c r="K3" s="194"/>
+      <x:c r="L3" s="194"/>
+      <x:c r="M3" s="194"/>
+      <x:c r="N3" s="194"/>
+      <x:c r="O3" s="194"/>
+      <x:c r="P3" s="194"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="102" t="str">
-        <x:v>유행 사건</x:v>
-      </x:c>
-      <x:c r="B4" s="104" t="n">
+      <x:c r="A4" s="184"/>
+      <x:c r="B4" s="184"/>
+      <x:c r="C4" s="184"/>
+      <x:c r="D4" s="184"/>
+      <x:c r="E4" s="184"/>
+      <x:c r="F4" s="184"/>
+      <x:c r="G4" s="184"/>
+      <x:c r="H4" s="184"/>
+      <x:c r="I4" s="184"/>
+      <x:c r="J4" s="184"/>
+      <x:c r="K4" s="184"/>
+      <x:c r="L4" s="184"/>
+      <x:c r="M4" s="184"/>
+      <x:c r="N4" s="184"/>
+      <x:c r="O4" s="184"/>
+      <x:c r="P4" s="184"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="496" t="str">
+        <x:v>전체 유행 사건</x:v>
+      </x:c>
+      <x:c r="B5" s="497"/>
+      <x:c r="C5" s="498"/>
+      <x:c r="D5" s="496" t="str">
+        <x:v>주가 반응 확인</x:v>
+      </x:c>
+      <x:c r="E5" s="497"/>
+      <x:c r="F5" s="498"/>
+      <x:c r="G5" s="496" t="str">
+        <x:v>후속 조사 후보</x:v>
+      </x:c>
+      <x:c r="H5" s="497"/>
+      <x:c r="I5" s="498"/>
+      <x:c r="J5" s="496" t="str">
+        <x:v>가장 큰 카테고리</x:v>
+      </x:c>
+      <x:c r="K5" s="497"/>
+      <x:c r="L5" s="498"/>
+      <x:c r="M5" s="496" t="str">
+        <x:v>가장 많은 연도</x:v>
+      </x:c>
+      <x:c r="N5" s="497"/>
+      <x:c r="O5" s="497"/>
+      <x:c r="P5" s="498"/>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="519" t="n">
         <x:f>COUNTA('01_유행이벤트'!$A$6:$A$303)</x:f>
         <x:v>298</x:v>
       </x:c>
-      <x:c r="C4" s="102" t="str">
-        <x:v>주가 연결 사건</x:v>
-      </x:c>
-      <x:c r="D4" s="104" t="n">
+      <x:c r="B6" s="520"/>
+      <x:c r="C6" s="521"/>
+      <x:c r="D6" s="559" t="n">
         <x:f>COUNTIF('01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E4" s="102" t="str">
-        <x:v>주가 미연결·미확인</x:v>
-      </x:c>
-      <x:c r="F4" s="104" t="n">
+      <x:c r="E6" s="560"/>
+      <x:c r="F6" s="561"/>
+      <x:c r="G6" s="585" t="n">
         <x:f>COUNTIF('01_유행이벤트'!$I$6:$I$303,"주가 미확인·연결 전")</x:f>
         <x:v>228</x:v>
       </x:c>
-      <x:c r="G4" s="102" t="str">
-        <x:v>종목 반응 행</x:v>
-      </x:c>
-      <x:c r="H4" s="104" t="n">
-        <x:f>COUNTA('02_종목반응'!$A$6:$A$166)</x:f>
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="I4" s="102" t="str">
-        <x:v>출처</x:v>
-      </x:c>
-      <x:c r="J4" s="104" t="n">
-        <x:f>COUNTA('03_출처'!$A$5:$A$136)</x:f>
-        <x:v>132</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="107" t="str">
-        <x:v>원장 구성</x:v>
-      </x:c>
-      <x:c r="B6" s="107"/>
-      <x:c r="C6" s="107"/>
-      <x:c r="D6" s="107"/>
-      <x:c r="E6" s="107"/>
-      <x:c r="F6" s="107" t="str">
-        <x:v>해석 원칙</x:v>
-      </x:c>
-      <x:c r="G6" s="107"/>
-      <x:c r="H6" s="107"/>
-      <x:c r="I6" s="107"/>
-      <x:c r="J6" s="107"/>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="113" t="str">
-        <x:v>01 유행이벤트</x:v>
-      </x:c>
-      <x:c r="B7" s="111" t="str">
-        <x:v>연도 내림차순 → 대분류 → 소분류 → 사건명</x:v>
-      </x:c>
-      <x:c r="C7" s="111"/>
-      <x:c r="D7" s="111"/>
-      <x:c r="E7" s="111"/>
-      <x:c r="F7" s="116" t="str">
+      <x:c r="H6" s="586"/>
+      <x:c r="I6" s="587"/>
+      <x:c r="J6" s="611" t="str">
+        <x:f>INDEX($D$49:$D$57,MATCH(MAX($E$49:$E$57),$E$49:$E$57,0))</x:f>
+        <x:v>콘텐츠·엔터</x:v>
+      </x:c>
+      <x:c r="K6" s="612"/>
+      <x:c r="L6" s="613"/>
+      <x:c r="M6" s="643" t="n">
+        <x:f>INDEX($A$49:$A$66,MATCH(MAX($B$49:$B$66),$B$49:$B$66,0))</x:f>
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="N6" s="644"/>
+      <x:c r="O6" s="644"/>
+      <x:c r="P6" s="645"/>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="522"/>
+      <x:c r="B7" s="523"/>
+      <x:c r="C7" s="524"/>
+      <x:c r="D7" s="562"/>
+      <x:c r="E7" s="563"/>
+      <x:c r="F7" s="564"/>
+      <x:c r="G7" s="588"/>
+      <x:c r="H7" s="589"/>
+      <x:c r="I7" s="590"/>
+      <x:c r="J7" s="614"/>
+      <x:c r="K7" s="615"/>
+      <x:c r="L7" s="616"/>
+      <x:c r="M7" s="646"/>
+      <x:c r="N7" s="647"/>
+      <x:c r="O7" s="647"/>
+      <x:c r="P7" s="648"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="536" t="str">
+        <x:f>"2009~2026 · 출처 "&amp;COUNTA('03_출처'!$A$5:$A$136)&amp;"개"</x:f>
+        <x:v>2009~2026 · 출처 132개</x:v>
+      </x:c>
+      <x:c r="B8" s="537"/>
+      <x:c r="C8" s="538"/>
+      <x:c r="D8" s="536" t="str">
+        <x:f>"전체의 "&amp;TEXT(D6/A6,"0.0%")</x:f>
+        <x:v>전체의 23.5%</x:v>
+      </x:c>
+      <x:c r="E8" s="537"/>
+      <x:c r="F8" s="538"/>
+      <x:c r="G8" s="536" t="str">
+        <x:f>"전체의 "&amp;TEXT(G6/A6,"0.0%")</x:f>
+        <x:v>전체의 76.5%</x:v>
+      </x:c>
+      <x:c r="H8" s="537"/>
+      <x:c r="I8" s="538"/>
+      <x:c r="J8" s="536" t="str">
+        <x:f>MAX($E$49:$E$57)&amp;"건 · "&amp;TEXT(MAX($E$49:$E$57)/A6,"0.0%")</x:f>
+        <x:v>89건 · 29.9%</x:v>
+      </x:c>
+      <x:c r="K8" s="537"/>
+      <x:c r="L8" s="538"/>
+      <x:c r="M8" s="536" t="str">
+        <x:f>MAX($B$49:$B$66)&amp;"건 · 2026년은 진행 중"</x:f>
+        <x:v>27건 · 2026년은 진행 중</x:v>
+      </x:c>
+      <x:c r="N8" s="537"/>
+      <x:c r="O8" s="537"/>
+      <x:c r="P8" s="538"/>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="184"/>
+      <x:c r="B9" s="184"/>
+      <x:c r="C9" s="184"/>
+      <x:c r="D9" s="184"/>
+      <x:c r="E9" s="184"/>
+      <x:c r="F9" s="184"/>
+      <x:c r="G9" s="184"/>
+      <x:c r="H9" s="184"/>
+      <x:c r="I9" s="184"/>
+      <x:c r="J9" s="184"/>
+      <x:c r="K9" s="184"/>
+      <x:c r="L9" s="184"/>
+      <x:c r="M9" s="184"/>
+      <x:c r="N9" s="184"/>
+      <x:c r="O9" s="184"/>
+      <x:c r="P9" s="184"/>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="651" t="str">
+        <x:v>데이터가 말하는 세 가지</x:v>
+      </x:c>
+      <x:c r="B10" s="651"/>
+      <x:c r="C10" s="651"/>
+      <x:c r="D10" s="651"/>
+      <x:c r="E10" s="651"/>
+      <x:c r="F10" s="651"/>
+      <x:c r="G10" s="651"/>
+      <x:c r="H10" s="651"/>
+      <x:c r="I10" s="651"/>
+      <x:c r="J10" s="651"/>
+      <x:c r="K10" s="651"/>
+      <x:c r="L10" s="651"/>
+      <x:c r="M10" s="651"/>
+      <x:c r="N10" s="651"/>
+      <x:c r="O10" s="651"/>
+      <x:c r="P10" s="651"/>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="672" t="str">
+        <x:f>"① 콘텐츠·엔터 "&amp;E49&amp;"건 + 식품·음료 "&amp;E50&amp;"건 = 전체 "&amp;TEXT((E49+E50)/A6,"0.0%")</x:f>
+        <x:v>① 콘텐츠·엔터 89건 + 식품·음료 76건 = 전체 55.4%</x:v>
+      </x:c>
+      <x:c r="B11" s="673"/>
+      <x:c r="C11" s="673"/>
+      <x:c r="D11" s="673"/>
+      <x:c r="E11" s="674"/>
+      <x:c r="F11" s="697" t="str">
+        <x:f>"② 주가 반응 확인 "&amp;D6&amp;"건보다 조사 대기 "&amp;G6&amp;"건이 "&amp;TEXT(G6/D6,"0.0x")&amp;" 많음"</x:f>
+        <x:v>② 주가 반응 확인 70건보다 조사 대기 228건이 3.3x 많음</x:v>
+      </x:c>
+      <x:c r="G11" s="698"/>
+      <x:c r="H11" s="698"/>
+      <x:c r="I11" s="698"/>
+      <x:c r="J11" s="699"/>
+      <x:c r="K11" s="723" t="str">
+        <x:f>"③ 최다 기록 연도 "&amp;M6&amp;"년 "&amp;MAX($B$49:$B$66)&amp;"건 · 최근 기록 집중"</x:f>
+        <x:v>③ 최다 기록 연도 2023년 27건 · 최근 기록 집중</x:v>
+      </x:c>
+      <x:c r="L11" s="724"/>
+      <x:c r="M11" s="724"/>
+      <x:c r="N11" s="724"/>
+      <x:c r="O11" s="724"/>
+      <x:c r="P11" s="725"/>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="675"/>
+      <x:c r="B12" s="676"/>
+      <x:c r="C12" s="676"/>
+      <x:c r="D12" s="676"/>
+      <x:c r="E12" s="677"/>
+      <x:c r="F12" s="700"/>
+      <x:c r="G12" s="701"/>
+      <x:c r="H12" s="701"/>
+      <x:c r="I12" s="701"/>
+      <x:c r="J12" s="702"/>
+      <x:c r="K12" s="726"/>
+      <x:c r="L12" s="727"/>
+      <x:c r="M12" s="727"/>
+      <x:c r="N12" s="727"/>
+      <x:c r="O12" s="727"/>
+      <x:c r="P12" s="728"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="184"/>
+      <x:c r="B13" s="184"/>
+      <x:c r="C13" s="184"/>
+      <x:c r="D13" s="184"/>
+      <x:c r="E13" s="184"/>
+      <x:c r="F13" s="184"/>
+      <x:c r="G13" s="184"/>
+      <x:c r="H13" s="184"/>
+      <x:c r="I13" s="184"/>
+      <x:c r="J13" s="184"/>
+      <x:c r="K13" s="184"/>
+      <x:c r="L13" s="184"/>
+      <x:c r="M13" s="184"/>
+      <x:c r="N13" s="184"/>
+      <x:c r="O13" s="184"/>
+      <x:c r="P13" s="184"/>
+    </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="184"/>
+      <x:c r="B14" s="184"/>
+      <x:c r="C14" s="184"/>
+      <x:c r="D14" s="184"/>
+      <x:c r="E14" s="184"/>
+      <x:c r="F14" s="184"/>
+      <x:c r="G14" s="184"/>
+      <x:c r="H14" s="184"/>
+      <x:c r="I14" s="184"/>
+      <x:c r="J14" s="184"/>
+      <x:c r="K14" s="184"/>
+      <x:c r="L14" s="184"/>
+      <x:c r="M14" s="184"/>
+      <x:c r="N14" s="184"/>
+      <x:c r="O14" s="184"/>
+      <x:c r="P14" s="184"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="184"/>
+      <x:c r="B15" s="184"/>
+      <x:c r="C15" s="184"/>
+      <x:c r="D15" s="184"/>
+      <x:c r="E15" s="184"/>
+      <x:c r="F15" s="184"/>
+      <x:c r="G15" s="184"/>
+      <x:c r="H15" s="184"/>
+      <x:c r="I15" s="184"/>
+      <x:c r="J15" s="184"/>
+      <x:c r="K15" s="184"/>
+      <x:c r="L15" s="184"/>
+      <x:c r="M15" s="184"/>
+      <x:c r="N15" s="184"/>
+      <x:c r="O15" s="184"/>
+      <x:c r="P15" s="184"/>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="184"/>
+      <x:c r="B16" s="184"/>
+      <x:c r="C16" s="184"/>
+      <x:c r="D16" s="184"/>
+      <x:c r="E16" s="184"/>
+      <x:c r="F16" s="184"/>
+      <x:c r="G16" s="184"/>
+      <x:c r="H16" s="184"/>
+      <x:c r="I16" s="184"/>
+      <x:c r="J16" s="184"/>
+      <x:c r="K16" s="184"/>
+      <x:c r="L16" s="184"/>
+      <x:c r="M16" s="184"/>
+      <x:c r="N16" s="184"/>
+      <x:c r="O16" s="184"/>
+      <x:c r="P16" s="184"/>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="184"/>
+      <x:c r="B17" s="184"/>
+      <x:c r="C17" s="184"/>
+      <x:c r="D17" s="184"/>
+      <x:c r="E17" s="184"/>
+      <x:c r="F17" s="184"/>
+      <x:c r="G17" s="184"/>
+      <x:c r="H17" s="184"/>
+      <x:c r="I17" s="184"/>
+      <x:c r="J17" s="184"/>
+      <x:c r="K17" s="184"/>
+      <x:c r="L17" s="184"/>
+      <x:c r="M17" s="184"/>
+      <x:c r="N17" s="184"/>
+      <x:c r="O17" s="184"/>
+      <x:c r="P17" s="184"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="184"/>
+      <x:c r="B18" s="184"/>
+      <x:c r="C18" s="184"/>
+      <x:c r="D18" s="184"/>
+      <x:c r="E18" s="184"/>
+      <x:c r="F18" s="184"/>
+      <x:c r="G18" s="184"/>
+      <x:c r="H18" s="184"/>
+      <x:c r="I18" s="184"/>
+      <x:c r="J18" s="184"/>
+      <x:c r="K18" s="184"/>
+      <x:c r="L18" s="184"/>
+      <x:c r="M18" s="184"/>
+      <x:c r="N18" s="184"/>
+      <x:c r="O18" s="184"/>
+      <x:c r="P18" s="184"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="184"/>
+      <x:c r="B19" s="184"/>
+      <x:c r="C19" s="184"/>
+      <x:c r="D19" s="184"/>
+      <x:c r="E19" s="184"/>
+      <x:c r="F19" s="184"/>
+      <x:c r="G19" s="184"/>
+      <x:c r="H19" s="184"/>
+      <x:c r="I19" s="184"/>
+      <x:c r="J19" s="184"/>
+      <x:c r="K19" s="184"/>
+      <x:c r="L19" s="184"/>
+      <x:c r="M19" s="184"/>
+      <x:c r="N19" s="184"/>
+      <x:c r="O19" s="184"/>
+      <x:c r="P19" s="184"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="184"/>
+      <x:c r="B20" s="184"/>
+      <x:c r="C20" s="184"/>
+      <x:c r="D20" s="184"/>
+      <x:c r="E20" s="184"/>
+      <x:c r="F20" s="184"/>
+      <x:c r="G20" s="184"/>
+      <x:c r="H20" s="184"/>
+      <x:c r="I20" s="184"/>
+      <x:c r="J20" s="184"/>
+      <x:c r="K20" s="184"/>
+      <x:c r="L20" s="184"/>
+      <x:c r="M20" s="184"/>
+      <x:c r="N20" s="184"/>
+      <x:c r="O20" s="184"/>
+      <x:c r="P20" s="184"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="184"/>
+      <x:c r="B21" s="184"/>
+      <x:c r="C21" s="184"/>
+      <x:c r="D21" s="184"/>
+      <x:c r="E21" s="184"/>
+      <x:c r="F21" s="184"/>
+      <x:c r="G21" s="184"/>
+      <x:c r="H21" s="184"/>
+      <x:c r="I21" s="184"/>
+      <x:c r="J21" s="184"/>
+      <x:c r="K21" s="184"/>
+      <x:c r="L21" s="184"/>
+      <x:c r="M21" s="184"/>
+      <x:c r="N21" s="184"/>
+      <x:c r="O21" s="184"/>
+      <x:c r="P21" s="184"/>
+    </x:row>
+    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="A22" s="184"/>
+      <x:c r="B22" s="184"/>
+      <x:c r="C22" s="184"/>
+      <x:c r="D22" s="184"/>
+      <x:c r="E22" s="184"/>
+      <x:c r="F22" s="184"/>
+      <x:c r="G22" s="184"/>
+      <x:c r="H22" s="184"/>
+      <x:c r="I22" s="184"/>
+      <x:c r="J22" s="184"/>
+      <x:c r="K22" s="184"/>
+      <x:c r="L22" s="184"/>
+      <x:c r="M22" s="184"/>
+      <x:c r="N22" s="184"/>
+      <x:c r="O22" s="184"/>
+      <x:c r="P22" s="184"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="184"/>
+      <x:c r="B23" s="184"/>
+      <x:c r="C23" s="184"/>
+      <x:c r="D23" s="184"/>
+      <x:c r="E23" s="184"/>
+      <x:c r="F23" s="184"/>
+      <x:c r="G23" s="184"/>
+      <x:c r="H23" s="184"/>
+      <x:c r="I23" s="184"/>
+      <x:c r="J23" s="184"/>
+      <x:c r="K23" s="184"/>
+      <x:c r="L23" s="184"/>
+      <x:c r="M23" s="184"/>
+      <x:c r="N23" s="184"/>
+      <x:c r="O23" s="184"/>
+      <x:c r="P23" s="184"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="184"/>
+      <x:c r="B24" s="184"/>
+      <x:c r="C24" s="184"/>
+      <x:c r="D24" s="184"/>
+      <x:c r="E24" s="184"/>
+      <x:c r="F24" s="184"/>
+      <x:c r="G24" s="184"/>
+      <x:c r="H24" s="184"/>
+      <x:c r="I24" s="184"/>
+      <x:c r="J24" s="184"/>
+      <x:c r="K24" s="184"/>
+      <x:c r="L24" s="184"/>
+      <x:c r="M24" s="184"/>
+      <x:c r="N24" s="184"/>
+      <x:c r="O24" s="184"/>
+      <x:c r="P24" s="184"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="184"/>
+      <x:c r="B25" s="184"/>
+      <x:c r="C25" s="184"/>
+      <x:c r="D25" s="184"/>
+      <x:c r="E25" s="184"/>
+      <x:c r="F25" s="184"/>
+      <x:c r="G25" s="184"/>
+      <x:c r="H25" s="184"/>
+      <x:c r="I25" s="184"/>
+      <x:c r="J25" s="184"/>
+      <x:c r="K25" s="184"/>
+      <x:c r="L25" s="184"/>
+      <x:c r="M25" s="184"/>
+      <x:c r="N25" s="184"/>
+      <x:c r="O25" s="184"/>
+      <x:c r="P25" s="184"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="184"/>
+      <x:c r="B26" s="184"/>
+      <x:c r="C26" s="184"/>
+      <x:c r="D26" s="184"/>
+      <x:c r="E26" s="184"/>
+      <x:c r="F26" s="184"/>
+      <x:c r="G26" s="184"/>
+      <x:c r="H26" s="184"/>
+      <x:c r="I26" s="184"/>
+      <x:c r="J26" s="184"/>
+      <x:c r="K26" s="184"/>
+      <x:c r="L26" s="184"/>
+      <x:c r="M26" s="184"/>
+      <x:c r="N26" s="184"/>
+      <x:c r="O26" s="184"/>
+      <x:c r="P26" s="184"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="184"/>
+      <x:c r="B27" s="184"/>
+      <x:c r="C27" s="184"/>
+      <x:c r="D27" s="184"/>
+      <x:c r="E27" s="184"/>
+      <x:c r="F27" s="184"/>
+      <x:c r="G27" s="184"/>
+      <x:c r="H27" s="184"/>
+      <x:c r="I27" s="184"/>
+      <x:c r="J27" s="184"/>
+      <x:c r="K27" s="184"/>
+      <x:c r="L27" s="184"/>
+      <x:c r="M27" s="184"/>
+      <x:c r="N27" s="184"/>
+      <x:c r="O27" s="184"/>
+      <x:c r="P27" s="184"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="184"/>
+      <x:c r="B28" s="184"/>
+      <x:c r="C28" s="184"/>
+      <x:c r="D28" s="184"/>
+      <x:c r="E28" s="184"/>
+      <x:c r="F28" s="184"/>
+      <x:c r="G28" s="184"/>
+      <x:c r="H28" s="184"/>
+      <x:c r="I28" s="184"/>
+      <x:c r="J28" s="184"/>
+      <x:c r="K28" s="184"/>
+      <x:c r="L28" s="184"/>
+      <x:c r="M28" s="184"/>
+      <x:c r="N28" s="184"/>
+      <x:c r="O28" s="184"/>
+      <x:c r="P28" s="184"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="184"/>
+      <x:c r="B29" s="184"/>
+      <x:c r="C29" s="184"/>
+      <x:c r="D29" s="184"/>
+      <x:c r="E29" s="184"/>
+      <x:c r="F29" s="184"/>
+      <x:c r="G29" s="184"/>
+      <x:c r="H29" s="184"/>
+      <x:c r="I29" s="184"/>
+      <x:c r="J29" s="184"/>
+      <x:c r="K29" s="184"/>
+      <x:c r="L29" s="184"/>
+      <x:c r="M29" s="184"/>
+      <x:c r="N29" s="184"/>
+      <x:c r="O29" s="184"/>
+      <x:c r="P29" s="184"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="184"/>
+      <x:c r="B30" s="184"/>
+      <x:c r="C30" s="184"/>
+      <x:c r="D30" s="184"/>
+      <x:c r="E30" s="184"/>
+      <x:c r="F30" s="184"/>
+      <x:c r="G30" s="184"/>
+      <x:c r="H30" s="184"/>
+      <x:c r="I30" s="184"/>
+      <x:c r="J30" s="184"/>
+      <x:c r="K30" s="184"/>
+      <x:c r="L30" s="184"/>
+      <x:c r="M30" s="184"/>
+      <x:c r="N30" s="184"/>
+      <x:c r="O30" s="184"/>
+      <x:c r="P30" s="184"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="184"/>
+      <x:c r="B31" s="184"/>
+      <x:c r="C31" s="184"/>
+      <x:c r="D31" s="184"/>
+      <x:c r="E31" s="184"/>
+      <x:c r="F31" s="184"/>
+      <x:c r="G31" s="184"/>
+      <x:c r="H31" s="184"/>
+      <x:c r="I31" s="184"/>
+      <x:c r="J31" s="184"/>
+      <x:c r="K31" s="184"/>
+      <x:c r="L31" s="184"/>
+      <x:c r="M31" s="184"/>
+      <x:c r="N31" s="184"/>
+      <x:c r="O31" s="184"/>
+      <x:c r="P31" s="184"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="184"/>
+      <x:c r="B32" s="184"/>
+      <x:c r="C32" s="184"/>
+      <x:c r="D32" s="184"/>
+      <x:c r="E32" s="184"/>
+      <x:c r="F32" s="184"/>
+      <x:c r="G32" s="184"/>
+      <x:c r="H32" s="184"/>
+      <x:c r="I32" s="184"/>
+      <x:c r="J32" s="184"/>
+      <x:c r="K32" s="184"/>
+      <x:c r="L32" s="184"/>
+      <x:c r="M32" s="184"/>
+      <x:c r="N32" s="184"/>
+      <x:c r="O32" s="184"/>
+      <x:c r="P32" s="184"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="184"/>
+      <x:c r="B33" s="184"/>
+      <x:c r="C33" s="184"/>
+      <x:c r="D33" s="184"/>
+      <x:c r="E33" s="184"/>
+      <x:c r="F33" s="184"/>
+      <x:c r="G33" s="184"/>
+      <x:c r="H33" s="184"/>
+      <x:c r="I33" s="184"/>
+      <x:c r="J33" s="184"/>
+      <x:c r="K33" s="184"/>
+      <x:c r="L33" s="184"/>
+      <x:c r="M33" s="184"/>
+      <x:c r="N33" s="184"/>
+      <x:c r="O33" s="184"/>
+      <x:c r="P33" s="184"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="184"/>
+      <x:c r="B34" s="184"/>
+      <x:c r="C34" s="184"/>
+      <x:c r="D34" s="184"/>
+      <x:c r="E34" s="184"/>
+      <x:c r="F34" s="184"/>
+      <x:c r="G34" s="184"/>
+      <x:c r="H34" s="184"/>
+      <x:c r="I34" s="184"/>
+      <x:c r="J34" s="184"/>
+      <x:c r="K34" s="184"/>
+      <x:c r="L34" s="184"/>
+      <x:c r="M34" s="184"/>
+      <x:c r="N34" s="184"/>
+      <x:c r="O34" s="184"/>
+      <x:c r="P34" s="184"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="184"/>
+      <x:c r="B35" s="184"/>
+      <x:c r="C35" s="184"/>
+      <x:c r="D35" s="184"/>
+      <x:c r="E35" s="184"/>
+      <x:c r="F35" s="184"/>
+      <x:c r="G35" s="184"/>
+      <x:c r="H35" s="184"/>
+      <x:c r="I35" s="184"/>
+      <x:c r="J35" s="184"/>
+      <x:c r="K35" s="184"/>
+      <x:c r="L35" s="184"/>
+      <x:c r="M35" s="184"/>
+      <x:c r="N35" s="184"/>
+      <x:c r="O35" s="184"/>
+      <x:c r="P35" s="184"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="184"/>
+      <x:c r="B36" s="184"/>
+      <x:c r="C36" s="184"/>
+      <x:c r="D36" s="184"/>
+      <x:c r="E36" s="184"/>
+      <x:c r="F36" s="184"/>
+      <x:c r="G36" s="184"/>
+      <x:c r="H36" s="184"/>
+      <x:c r="I36" s="184"/>
+      <x:c r="J36" s="184"/>
+      <x:c r="K36" s="184"/>
+      <x:c r="L36" s="184"/>
+      <x:c r="M36" s="184"/>
+      <x:c r="N36" s="184"/>
+      <x:c r="O36" s="184"/>
+      <x:c r="P36" s="184"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="184"/>
+      <x:c r="B37" s="184"/>
+      <x:c r="C37" s="184"/>
+      <x:c r="D37" s="184"/>
+      <x:c r="E37" s="184"/>
+      <x:c r="F37" s="184"/>
+      <x:c r="G37" s="184"/>
+      <x:c r="H37" s="184"/>
+      <x:c r="I37" s="184"/>
+      <x:c r="J37" s="184"/>
+      <x:c r="K37" s="184"/>
+      <x:c r="L37" s="184"/>
+      <x:c r="M37" s="184"/>
+      <x:c r="N37" s="184"/>
+      <x:c r="O37" s="184"/>
+      <x:c r="P37" s="184"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="184"/>
+      <x:c r="B38" s="184"/>
+      <x:c r="C38" s="184"/>
+      <x:c r="D38" s="184"/>
+      <x:c r="E38" s="184"/>
+      <x:c r="F38" s="184"/>
+      <x:c r="G38" s="184"/>
+      <x:c r="H38" s="184"/>
+      <x:c r="I38" s="184"/>
+      <x:c r="J38" s="184"/>
+      <x:c r="K38" s="184"/>
+      <x:c r="L38" s="184"/>
+      <x:c r="M38" s="184"/>
+      <x:c r="N38" s="184"/>
+      <x:c r="O38" s="184"/>
+      <x:c r="P38" s="184"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="184"/>
+      <x:c r="B39" s="184"/>
+      <x:c r="C39" s="184"/>
+      <x:c r="D39" s="184"/>
+      <x:c r="E39" s="184"/>
+      <x:c r="F39" s="184"/>
+      <x:c r="G39" s="184"/>
+      <x:c r="H39" s="184"/>
+      <x:c r="I39" s="184"/>
+      <x:c r="J39" s="184"/>
+      <x:c r="K39" s="184"/>
+      <x:c r="L39" s="184"/>
+      <x:c r="M39" s="184"/>
+      <x:c r="N39" s="184"/>
+      <x:c r="O39" s="184"/>
+      <x:c r="P39" s="184"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="184"/>
+      <x:c r="B40" s="184"/>
+      <x:c r="C40" s="184"/>
+      <x:c r="D40" s="184"/>
+      <x:c r="E40" s="184"/>
+      <x:c r="F40" s="184"/>
+      <x:c r="G40" s="184"/>
+      <x:c r="H40" s="184"/>
+      <x:c r="I40" s="184"/>
+      <x:c r="J40" s="184"/>
+      <x:c r="K40" s="184"/>
+      <x:c r="L40" s="184"/>
+      <x:c r="M40" s="184"/>
+      <x:c r="N40" s="184"/>
+      <x:c r="O40" s="184"/>
+      <x:c r="P40" s="184"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="184"/>
+      <x:c r="B41" s="184"/>
+      <x:c r="C41" s="184"/>
+      <x:c r="D41" s="184"/>
+      <x:c r="E41" s="184"/>
+      <x:c r="F41" s="184"/>
+      <x:c r="G41" s="184"/>
+      <x:c r="H41" s="184"/>
+      <x:c r="I41" s="184"/>
+      <x:c r="J41" s="184"/>
+      <x:c r="K41" s="184"/>
+      <x:c r="L41" s="184"/>
+      <x:c r="M41" s="184"/>
+      <x:c r="N41" s="184"/>
+      <x:c r="O41" s="184"/>
+      <x:c r="P41" s="184"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="184"/>
+      <x:c r="B42" s="184"/>
+      <x:c r="C42" s="184"/>
+      <x:c r="D42" s="184"/>
+      <x:c r="E42" s="184"/>
+      <x:c r="F42" s="184"/>
+      <x:c r="G42" s="184"/>
+      <x:c r="H42" s="184"/>
+      <x:c r="I42" s="184"/>
+      <x:c r="J42" s="184"/>
+      <x:c r="K42" s="184"/>
+      <x:c r="L42" s="184"/>
+      <x:c r="M42" s="184"/>
+      <x:c r="N42" s="184"/>
+      <x:c r="O42" s="184"/>
+      <x:c r="P42" s="184"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="184"/>
+      <x:c r="B43" s="184"/>
+      <x:c r="C43" s="184"/>
+      <x:c r="D43" s="184"/>
+      <x:c r="E43" s="184"/>
+      <x:c r="F43" s="184"/>
+      <x:c r="G43" s="184"/>
+      <x:c r="H43" s="184"/>
+      <x:c r="I43" s="184"/>
+      <x:c r="J43" s="184"/>
+      <x:c r="K43" s="184"/>
+      <x:c r="L43" s="184"/>
+      <x:c r="M43" s="184"/>
+      <x:c r="N43" s="184"/>
+      <x:c r="O43" s="184"/>
+      <x:c r="P43" s="184"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="184"/>
+      <x:c r="B44" s="184"/>
+      <x:c r="C44" s="184"/>
+      <x:c r="D44" s="184"/>
+      <x:c r="E44" s="184"/>
+      <x:c r="F44" s="184"/>
+      <x:c r="G44" s="184"/>
+      <x:c r="H44" s="184"/>
+      <x:c r="I44" s="184"/>
+      <x:c r="J44" s="184"/>
+      <x:c r="K44" s="184"/>
+      <x:c r="L44" s="184"/>
+      <x:c r="M44" s="184"/>
+      <x:c r="N44" s="184"/>
+      <x:c r="O44" s="184"/>
+      <x:c r="P44" s="184"/>
+    </x:row>
+    <x:row r="45" ht="26" customHeight="1">
+      <x:c r="A45" s="780" t="str">
+        <x:v>주의: 본 대시보드는 공개 기록 기반 조사 현황입니다. 유행·검색·SNS 확산과 주가 반응의 인과관계를 단정하거나 매수를 권유하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="B45" s="780"/>
+      <x:c r="C45" s="780"/>
+      <x:c r="D45" s="780"/>
+      <x:c r="E45" s="780"/>
+      <x:c r="F45" s="780"/>
+      <x:c r="G45" s="780"/>
+      <x:c r="H45" s="780"/>
+      <x:c r="I45" s="780"/>
+      <x:c r="J45" s="780"/>
+      <x:c r="K45" s="780"/>
+      <x:c r="L45" s="780"/>
+      <x:c r="M45" s="780"/>
+      <x:c r="N45" s="780"/>
+      <x:c r="O45" s="780"/>
+      <x:c r="P45" s="780"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="184"/>
+      <x:c r="B46" s="184"/>
+      <x:c r="C46" s="184"/>
+      <x:c r="D46" s="184"/>
+      <x:c r="E46" s="184"/>
+      <x:c r="F46" s="184"/>
+      <x:c r="G46" s="184"/>
+      <x:c r="H46" s="184"/>
+      <x:c r="I46" s="184"/>
+      <x:c r="J46" s="184"/>
+      <x:c r="K46" s="184"/>
+      <x:c r="L46" s="184"/>
+      <x:c r="M46" s="184"/>
+      <x:c r="N46" s="184"/>
+      <x:c r="O46" s="184"/>
+      <x:c r="P46" s="184"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="730" t="str">
+        <x:v>차트 계산 근거 — 01 유행이벤트 시트와 수식으로 연결</x:v>
+      </x:c>
+      <x:c r="B47" s="730"/>
+      <x:c r="C47" s="730"/>
+      <x:c r="D47" s="730"/>
+      <x:c r="E47" s="730"/>
+      <x:c r="F47" s="730"/>
+      <x:c r="G47" s="730"/>
+      <x:c r="H47" s="730"/>
+      <x:c r="I47" s="730"/>
+      <x:c r="J47" s="730"/>
+      <x:c r="K47" s="730"/>
+      <x:c r="L47" s="730"/>
+      <x:c r="M47" s="730"/>
+      <x:c r="N47" s="730"/>
+      <x:c r="O47" s="730"/>
+      <x:c r="P47" s="730"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="733" t="str">
+        <x:v>연도</x:v>
+      </x:c>
+      <x:c r="B48" s="733" t="str">
+        <x:v>사건 수</x:v>
+      </x:c>
+      <x:c r="C48" s="184"/>
+      <x:c r="D48" s="733" t="str">
+        <x:v>대분류</x:v>
+      </x:c>
+      <x:c r="E48" s="733" t="str">
+        <x:v>전체 사건</x:v>
+      </x:c>
+      <x:c r="F48" s="733" t="str">
+        <x:v>주가 연결</x:v>
+      </x:c>
+      <x:c r="G48" s="733" t="str">
+        <x:v>연결률</x:v>
+      </x:c>
+      <x:c r="H48" s="184"/>
+      <x:c r="I48" s="733" t="str">
+        <x:v>주가 연결 상태</x:v>
+      </x:c>
+      <x:c r="J48" s="733" t="str">
+        <x:v>사건 수</x:v>
+      </x:c>
+      <x:c r="K48" s="733" t="str">
+        <x:v>대분류</x:v>
+      </x:c>
+      <x:c r="L48" s="733" t="str">
+        <x:v>주가 연결률</x:v>
+      </x:c>
+      <x:c r="M48" s="184"/>
+      <x:c r="N48" s="747" t="str">
+        <x:v>해석 주의</x:v>
+      </x:c>
+      <x:c r="O48" s="747"/>
+      <x:c r="P48" s="747"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="742" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="B49" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A49)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C49" s="184"/>
+      <x:c r="D49" s="737" t="str">
+        <x:v>콘텐츠·엔터</x:v>
+      </x:c>
+      <x:c r="E49" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D49)</x:f>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F49" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D49,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G49" s="744" t="n">
+        <x:f>IFERROR(F49/E49,0)</x:f>
+        <x:v>0.23595505617977527</x:v>
+      </x:c>
+      <x:c r="H49" s="184"/>
+      <x:c r="I49" s="737" t="str">
+        <x:v>주가 반응 기록 있음</x:v>
+      </x:c>
+      <x:c r="J49" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$I$6:$I$303,I49)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K49" s="737" t="str">
+        <x:f>D49</x:f>
+        <x:v>콘텐츠·엔터</x:v>
+      </x:c>
+      <x:c r="L49" s="744" t="n">
+        <x:f>G49</x:f>
+        <x:v>0.23595505617977527</x:v>
+      </x:c>
+      <x:c r="M49" s="184"/>
+      <x:c r="N49" s="768" t="str">
+        <x:v>• 연결률은 “주가 영향 확률”이 아니라 현재 원장에서 가격 근거까지 확보된 비중입니다.
+• 금융·시장현상은 5건뿐이므로 100% 수치를 일반화하면 안 됩니다.
+• 2026년은 진행 중인 연도라 과거 완결 연도와 직접 비교할 때 주의합니다.</x:v>
+      </x:c>
+      <x:c r="O49" s="769"/>
+      <x:c r="P49" s="770"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="742" t="str">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="B50" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A50)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="184"/>
+      <x:c r="D50" s="737" t="str">
+        <x:v>식품·음료</x:v>
+      </x:c>
+      <x:c r="E50" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D50)</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F50" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D50,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G50" s="744" t="n">
+        <x:f>IFERROR(F50/E50,0)</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H50" s="184"/>
+      <x:c r="I50" s="737" t="str">
+        <x:v>주가 미확인·연결 전</x:v>
+      </x:c>
+      <x:c r="J50" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$I$6:$I$303,I50)</x:f>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="K50" s="737" t="str">
+        <x:f>D50</x:f>
+        <x:v>식품·음료</x:v>
+      </x:c>
+      <x:c r="L50" s="744" t="n">
+        <x:f>G50</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="M50" s="184"/>
+      <x:c r="N50" s="771"/>
+      <x:c r="O50" s="772"/>
+      <x:c r="P50" s="773"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="742" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B51" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A51)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C51" s="184"/>
+      <x:c r="D51" s="737" t="str">
+        <x:v>디지털·플랫폼</x:v>
+      </x:c>
+      <x:c r="E51" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D51)</x:f>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F51" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D51,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G51" s="744" t="n">
+        <x:f>IFERROR(F51/E51,0)</x:f>
+        <x:v>0.11627906976744186</x:v>
+      </x:c>
+      <x:c r="H51" s="184"/>
+      <x:c r="I51" s="184"/>
+      <x:c r="J51" s="184"/>
+      <x:c r="K51" s="737" t="str">
+        <x:f>D51</x:f>
+        <x:v>디지털·플랫폼</x:v>
+      </x:c>
+      <x:c r="L51" s="744" t="n">
+        <x:f>G51</x:f>
+        <x:v>0.11627906976744186</x:v>
+      </x:c>
+      <x:c r="M51" s="184"/>
+      <x:c r="N51" s="771"/>
+      <x:c r="O51" s="772"/>
+      <x:c r="P51" s="773"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="742" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B52" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A52)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C52" s="184"/>
+      <x:c r="D52" s="737" t="str">
+        <x:v>게임·e스포츠</x:v>
+      </x:c>
+      <x:c r="E52" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D52)</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F52" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D52,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G52" s="744" t="n">
+        <x:f>IFERROR(F52/E52,0)</x:f>
+        <x:v>0.08695652173913043</x:v>
+      </x:c>
+      <x:c r="H52" s="184"/>
+      <x:c r="I52" s="184"/>
+      <x:c r="J52" s="184"/>
+      <x:c r="K52" s="737" t="str">
+        <x:f>D52</x:f>
+        <x:v>게임·e스포츠</x:v>
+      </x:c>
+      <x:c r="L52" s="744" t="n">
+        <x:f>G52</x:f>
+        <x:v>0.08695652173913043</x:v>
+      </x:c>
+      <x:c r="M52" s="184"/>
+      <x:c r="N52" s="771"/>
+      <x:c r="O52" s="772"/>
+      <x:c r="P52" s="773"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="742" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B53" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A53)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C53" s="184"/>
+      <x:c r="D53" s="737" t="str">
+        <x:v>패션·뷰티</x:v>
+      </x:c>
+      <x:c r="E53" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D53)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F53" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D53,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G53" s="744" t="n">
+        <x:f>IFERROR(F53/E53,0)</x:f>
+        <x:v>0.15789473684210525</x:v>
+      </x:c>
+      <x:c r="H53" s="184"/>
+      <x:c r="I53" s="184"/>
+      <x:c r="J53" s="184"/>
+      <x:c r="K53" s="737" t="str">
+        <x:f>D53</x:f>
+        <x:v>패션·뷰티</x:v>
+      </x:c>
+      <x:c r="L53" s="744" t="n">
+        <x:f>G53</x:f>
+        <x:v>0.15789473684210525</x:v>
+      </x:c>
+      <x:c r="M53" s="184"/>
+      <x:c r="N53" s="771"/>
+      <x:c r="O53" s="772"/>
+      <x:c r="P53" s="773"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="742" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B54" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A54)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C54" s="184"/>
+      <x:c r="D54" s="737" t="str">
+        <x:v>생활·소비</x:v>
+      </x:c>
+      <x:c r="E54" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D54)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F54" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D54,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G54" s="744" t="n">
+        <x:f>IFERROR(F54/E54,0)</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="H54" s="184"/>
+      <x:c r="I54" s="184"/>
+      <x:c r="J54" s="184"/>
+      <x:c r="K54" s="737" t="str">
+        <x:f>D54</x:f>
+        <x:v>생활·소비</x:v>
+      </x:c>
+      <x:c r="L54" s="744" t="n">
+        <x:f>G54</x:f>
+        <x:v>0.3125</x:v>
+      </x:c>
+      <x:c r="M54" s="184"/>
+      <x:c r="N54" s="771"/>
+      <x:c r="O54" s="772"/>
+      <x:c r="P54" s="773"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="742" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B55" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A55)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C55" s="184"/>
+      <x:c r="D55" s="737" t="str">
+        <x:v>사회·온라인문화</x:v>
+      </x:c>
+      <x:c r="E55" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D55)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F55" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D55,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="111" t="str">
-        <x:v>유행 존재와 확산 이유를 먼저 확인</x:v>
-      </x:c>
-      <x:c r="H7" s="111"/>
-      <x:c r="I7" s="111"/>
-      <x:c r="J7" s="111"/>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="113" t="str">
-        <x:v>02 종목반응</x:v>
-      </x:c>
-      <x:c r="B8" s="111" t="str">
-        <x:v>연도 내림차순이며 사건과 동일한 대분류·소분류 적용</x:v>
-      </x:c>
-      <x:c r="C8" s="111"/>
-      <x:c r="D8" s="111"/>
-      <x:c r="E8" s="111"/>
-      <x:c r="F8" s="116" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G8" s="111" t="str">
-        <x:v>주가 미확인은 “영향 없음”이 아니라 후속 조사 대기 상태</x:v>
-      </x:c>
-      <x:c r="H8" s="111"/>
-      <x:c r="I8" s="111"/>
-      <x:c r="J8" s="111"/>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="113" t="str">
-        <x:v>03 출처</x:v>
-      </x:c>
-      <x:c r="B9" s="111" t="str">
-        <x:v>확인 가능한 발행일 기준 최신순, 출처ID는 고정</x:v>
-      </x:c>
-      <x:c r="C9" s="111"/>
-      <x:c r="D9" s="111"/>
-      <x:c r="E9" s="111"/>
-      <x:c r="F9" s="116" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G9" s="111" t="str">
-        <x:v>주가 반응 표에는 실제 가격·일자 근거가 있는 사례만 유지</x:v>
-      </x:c>
-      <x:c r="H9" s="111"/>
-      <x:c r="I9" s="111"/>
-      <x:c r="J9" s="111"/>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="113" t="str">
-        <x:v>04 판정기준</x:v>
-      </x:c>
-      <x:c r="B10" s="111" t="str">
-        <x:v>포함·연결 기준과 9개 대분류 체계를 함께 확인</x:v>
-      </x:c>
-      <x:c r="C10" s="111"/>
-      <x:c r="D10" s="111"/>
-      <x:c r="E10" s="111"/>
-      <x:c r="F10" s="116" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G10" s="111" t="str">
-        <x:v>같은 시기 실적·공시 등 동시 재료를 반드시 분리</x:v>
-      </x:c>
-      <x:c r="H10" s="111"/>
-      <x:c r="I10" s="111"/>
-      <x:c r="J10" s="111"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="113" t="str">
-        <x:v>포함</x:v>
-      </x:c>
-      <x:c r="B11" s="111" t="str">
-        <x:v>식품·음료, 콘텐츠·엔터, 디지털·플랫폼, 게임, 패션·뷰티, 생활, 스포츠, 온라인문화, 시장현상</x:v>
-      </x:c>
-      <x:c r="C11" s="111"/>
-      <x:c r="D11" s="111"/>
-      <x:c r="E11" s="111"/>
-      <x:c r="F11" s="116" t="str">
+      <x:c r="G55" s="744" t="n">
+        <x:f>IFERROR(F55/E55,0)</x:f>
+        <x:v>0.07142857142857142</x:v>
+      </x:c>
+      <x:c r="H55" s="184"/>
+      <x:c r="I55" s="184"/>
+      <x:c r="J55" s="184"/>
+      <x:c r="K55" s="737" t="str">
+        <x:f>D55</x:f>
+        <x:v>사회·온라인문화</x:v>
+      </x:c>
+      <x:c r="L55" s="744" t="n">
+        <x:f>G55</x:f>
+        <x:v>0.07142857142857142</x:v>
+      </x:c>
+      <x:c r="M55" s="184"/>
+      <x:c r="N55" s="771"/>
+      <x:c r="O55" s="772"/>
+      <x:c r="P55" s="773"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="742" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B56" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A56)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C56" s="184"/>
+      <x:c r="D56" s="737" t="str">
+        <x:v>스포츠·건강</x:v>
+      </x:c>
+      <x:c r="E56" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D56)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F56" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D56,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G56" s="744" t="n">
+        <x:f>IFERROR(F56/E56,0)</x:f>
+        <x:v>0.6923076923076923</x:v>
+      </x:c>
+      <x:c r="H56" s="184"/>
+      <x:c r="I56" s="184"/>
+      <x:c r="J56" s="184"/>
+      <x:c r="K56" s="737" t="str">
+        <x:f>D56</x:f>
+        <x:v>스포츠·건강</x:v>
+      </x:c>
+      <x:c r="L56" s="744" t="n">
+        <x:f>G56</x:f>
+        <x:v>0.6923076923076923</x:v>
+      </x:c>
+      <x:c r="M56" s="184"/>
+      <x:c r="N56" s="771"/>
+      <x:c r="O56" s="772"/>
+      <x:c r="P56" s="773"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="742" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B57" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A57)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C57" s="184"/>
+      <x:c r="D57" s="737" t="str">
+        <x:v>금융·시장현상</x:v>
+      </x:c>
+      <x:c r="E57" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$C$6:$C$303,D57)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G11" s="111" t="str">
-        <x:v>유행은 매수 신호가 아니라 기업 조사의 출발점</x:v>
-      </x:c>
-      <x:c r="H11" s="111"/>
-      <x:c r="I11" s="111"/>
-      <x:c r="J11" s="111"/>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="113" t="str">
-        <x:v>제외</x:v>
-      </x:c>
-      <x:c r="B12" s="111" t="str">
-        <x:v>정치인·선거·공약·정책·정부사업 테마</x:v>
-      </x:c>
-      <x:c r="C12" s="111"/>
-      <x:c r="D12" s="111"/>
-      <x:c r="E12" s="111"/>
-      <x:c r="F12" s="116" t="str">
-        <x:v>한계</x:v>
-      </x:c>
-      <x:c r="G12" s="111" t="str">
-        <x:v>삭제 게시물·비공개 커뮤니티 때문에 “완전 전수”는 불가능</x:v>
-      </x:c>
-      <x:c r="H12" s="111"/>
-      <x:c r="I12" s="111"/>
-      <x:c r="J12" s="111"/>
-    </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="118" t="str">
-        <x:v>연도별 유행 사건 수 — 최신 연도부터 확인</x:v>
-      </x:c>
-      <x:c r="B14" s="118"/>
-      <x:c r="C14" s="118"/>
-      <x:c r="D14" s="118"/>
-      <x:c r="E14" s="118"/>
-      <x:c r="F14" s="118"/>
-      <x:c r="G14" s="118"/>
-      <x:c r="H14" s="118"/>
-      <x:c r="I14" s="118"/>
-      <x:c r="J14" s="118"/>
-    </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="121" t="n">
+      <x:c r="F57" s="743" t="n">
+        <x:f>COUNTIFS('01_유행이벤트'!$C$6:$C$303,D57,'01_유행이벤트'!$I$6:$I$303,"주가 반응 기록 있음")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G57" s="744" t="n">
+        <x:f>IFERROR(F57/E57,0)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" s="184"/>
+      <x:c r="I57" s="184"/>
+      <x:c r="J57" s="184"/>
+      <x:c r="K57" s="737" t="str">
+        <x:f>D57</x:f>
+        <x:v>금융·시장현상</x:v>
+      </x:c>
+      <x:c r="L57" s="744" t="n">
+        <x:f>G57</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M57" s="184"/>
+      <x:c r="N57" s="774"/>
+      <x:c r="O57" s="775"/>
+      <x:c r="P57" s="776"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="742" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B58" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A58)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C58" s="184"/>
+      <x:c r="D58" s="184"/>
+      <x:c r="E58" s="184"/>
+      <x:c r="F58" s="184"/>
+      <x:c r="G58" s="184"/>
+      <x:c r="H58" s="184"/>
+      <x:c r="I58" s="184"/>
+      <x:c r="J58" s="184"/>
+      <x:c r="K58" s="184"/>
+      <x:c r="L58" s="184"/>
+      <x:c r="M58" s="184"/>
+      <x:c r="N58" s="184"/>
+      <x:c r="O58" s="184"/>
+      <x:c r="P58" s="184"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="742" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B59" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A59)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C59" s="184"/>
+      <x:c r="D59" s="184"/>
+      <x:c r="E59" s="184"/>
+      <x:c r="F59" s="184"/>
+      <x:c r="G59" s="184"/>
+      <x:c r="H59" s="184"/>
+      <x:c r="I59" s="184"/>
+      <x:c r="J59" s="184"/>
+      <x:c r="K59" s="184"/>
+      <x:c r="L59" s="184"/>
+      <x:c r="M59" s="184"/>
+      <x:c r="N59" s="184"/>
+      <x:c r="O59" s="184"/>
+      <x:c r="P59" s="184"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="742" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B60" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A60)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C60" s="184"/>
+      <x:c r="D60" s="184"/>
+      <x:c r="E60" s="184"/>
+      <x:c r="F60" s="184"/>
+      <x:c r="G60" s="184"/>
+      <x:c r="H60" s="184"/>
+      <x:c r="I60" s="184"/>
+      <x:c r="J60" s="184"/>
+      <x:c r="K60" s="184"/>
+      <x:c r="L60" s="184"/>
+      <x:c r="M60" s="184"/>
+      <x:c r="N60" s="184"/>
+      <x:c r="O60" s="184"/>
+      <x:c r="P60" s="184"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="742" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B61" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A61)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C61" s="184"/>
+      <x:c r="D61" s="184"/>
+      <x:c r="E61" s="184"/>
+      <x:c r="F61" s="184"/>
+      <x:c r="G61" s="184"/>
+      <x:c r="H61" s="184"/>
+      <x:c r="I61" s="184"/>
+      <x:c r="J61" s="184"/>
+      <x:c r="K61" s="184"/>
+      <x:c r="L61" s="184"/>
+      <x:c r="M61" s="184"/>
+      <x:c r="N61" s="184"/>
+      <x:c r="O61" s="184"/>
+      <x:c r="P61" s="184"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="742" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B62" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A62)</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C62" s="184"/>
+      <x:c r="D62" s="184"/>
+      <x:c r="E62" s="184"/>
+      <x:c r="F62" s="184"/>
+      <x:c r="G62" s="184"/>
+      <x:c r="H62" s="184"/>
+      <x:c r="I62" s="184"/>
+      <x:c r="J62" s="184"/>
+      <x:c r="K62" s="184"/>
+      <x:c r="L62" s="184"/>
+      <x:c r="M62" s="184"/>
+      <x:c r="N62" s="184"/>
+      <x:c r="O62" s="184"/>
+      <x:c r="P62" s="184"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="742" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B63" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A63)</x:f>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C63" s="184"/>
+      <x:c r="D63" s="184"/>
+      <x:c r="E63" s="184"/>
+      <x:c r="F63" s="184"/>
+      <x:c r="G63" s="184"/>
+      <x:c r="H63" s="184"/>
+      <x:c r="I63" s="184"/>
+      <x:c r="J63" s="184"/>
+      <x:c r="K63" s="184"/>
+      <x:c r="L63" s="184"/>
+      <x:c r="M63" s="184"/>
+      <x:c r="N63" s="184"/>
+      <x:c r="O63" s="184"/>
+      <x:c r="P63" s="184"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="742" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B64" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A64)</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C64" s="184"/>
+      <x:c r="D64" s="184"/>
+      <x:c r="E64" s="184"/>
+      <x:c r="F64" s="184"/>
+      <x:c r="G64" s="184"/>
+      <x:c r="H64" s="184"/>
+      <x:c r="I64" s="184"/>
+      <x:c r="J64" s="184"/>
+      <x:c r="K64" s="184"/>
+      <x:c r="L64" s="184"/>
+      <x:c r="M64" s="184"/>
+      <x:c r="N64" s="184"/>
+      <x:c r="O64" s="184"/>
+      <x:c r="P64" s="184"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="742" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B65" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A65)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C65" s="184"/>
+      <x:c r="D65" s="184"/>
+      <x:c r="E65" s="184"/>
+      <x:c r="F65" s="184"/>
+      <x:c r="G65" s="184"/>
+      <x:c r="H65" s="184"/>
+      <x:c r="I65" s="184"/>
+      <x:c r="J65" s="184"/>
+      <x:c r="K65" s="184"/>
+      <x:c r="L65" s="184"/>
+      <x:c r="M65" s="184"/>
+      <x:c r="N65" s="184"/>
+      <x:c r="O65" s="184"/>
+      <x:c r="P65" s="184"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="742" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="B16" s="121" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="C16" s="121" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="D16" s="121" t="n">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c r="E16" s="121" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="F16" s="121" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="G16" s="121" t="n">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c r="H16" s="121" t="n">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c r="I16" s="121" t="n">
-        <x:v>2018</x:v>
-      </x:c>
-      <x:c r="J16"/>
-    </x:row>
-    <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A16)</x:f>
+      <x:c r="B66" s="743" t="n">
+        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A66)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,B16)</x:f>
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,C16)</x:f>
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,D16)</x:f>
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,E16)</x:f>
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,F16)</x:f>
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,G16)</x:f>
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,H16)</x:f>
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I17" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,I16)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J17"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="121" t="n">
-        <x:v>2017</x:v>
-      </x:c>
-      <x:c r="B19" s="121" t="n">
-        <x:v>2016</x:v>
-      </x:c>
-      <x:c r="C19" s="121" t="n">
-        <x:v>2015</x:v>
-      </x:c>
-      <x:c r="D19" s="121" t="n">
-        <x:v>2014</x:v>
-      </x:c>
-      <x:c r="E19" s="121" t="n">
-        <x:v>2013</x:v>
-      </x:c>
-      <x:c r="F19" s="121" t="n">
-        <x:v>2012</x:v>
-      </x:c>
-      <x:c r="G19" s="121" t="n">
-        <x:v>2011</x:v>
-      </x:c>
-      <x:c r="H19" s="121" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="I19" s="121" t="n">
-        <x:v>2009</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,A19)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,B19)</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,C19)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,D19)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,E19)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,F19)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,G19)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,H19)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I20" s="125" t="n">
-        <x:f>COUNTIF('01_유행이벤트'!$B$6:$B$303,I19)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="34" customHeight="1">
-      <x:c r="A22" s="129" t="str">
-        <x:v>주의: 이 원장은 유행·검색·플랫폼 확산의 조사 자료이며 투자 추천이 아닙니다. 인과관계는 각 출처가 확인하는 범위까지만 표시합니다.</x:v>
-      </x:c>
-      <x:c r="B22" s="129"/>
-      <x:c r="C22" s="129"/>
-      <x:c r="D22" s="129"/>
-      <x:c r="E22" s="129"/>
-      <x:c r="F22" s="129"/>
-      <x:c r="G22" s="129"/>
-      <x:c r="H22" s="129"/>
-      <x:c r="I22" s="129"/>
-      <x:c r="J22" s="129"/>
+      <x:c r="C66" s="184"/>
+      <x:c r="D66" s="184"/>
+      <x:c r="E66" s="184"/>
+      <x:c r="F66" s="184"/>
+      <x:c r="G66" s="184"/>
+      <x:c r="H66" s="184"/>
+      <x:c r="I66" s="184"/>
+      <x:c r="J66" s="184"/>
+      <x:c r="K66" s="184"/>
+      <x:c r="L66" s="184"/>
+      <x:c r="M66" s="184"/>
+      <x:c r="N66" s="184"/>
+      <x:c r="O66" s="184"/>
+      <x:c r="P66" s="184"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="184"/>
+      <x:c r="B67" s="184"/>
+      <x:c r="C67" s="184"/>
+      <x:c r="D67" s="184"/>
+      <x:c r="E67" s="184"/>
+      <x:c r="F67" s="184"/>
+      <x:c r="G67" s="184"/>
+      <x:c r="H67" s="184"/>
+      <x:c r="I67" s="184"/>
+      <x:c r="J67" s="184"/>
+      <x:c r="K67" s="184"/>
+      <x:c r="L67" s="184"/>
+      <x:c r="M67" s="184"/>
+      <x:c r="N67" s="184"/>
+      <x:c r="O67" s="184"/>
+      <x:c r="P67" s="184"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:J1"/>
-    <x:mergeCell ref="A6:E6"/>
-    <x:mergeCell ref="F6:J6"/>
-    <x:mergeCell ref="A22:J22"/>
-    <x:mergeCell ref="B7:E7"/>
-    <x:mergeCell ref="G7:J7"/>
-    <x:mergeCell ref="B8:E8"/>
-    <x:mergeCell ref="G8:J8"/>
-    <x:mergeCell ref="B9:E9"/>
-    <x:mergeCell ref="G9:J9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="G10:J10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="G11:J11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="G12:J12"/>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="A14:J14"/>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:P2"/>
+    <x:mergeCell ref="A3:P3"/>
+    <x:mergeCell ref="A5:C5"/>
+    <x:mergeCell ref="A6:C7"/>
+    <x:mergeCell ref="A8:C8"/>
+    <x:mergeCell ref="D5:F5"/>
+    <x:mergeCell ref="D6:F7"/>
+    <x:mergeCell ref="D8:F8"/>
+    <x:mergeCell ref="G5:I5"/>
+    <x:mergeCell ref="G6:I7"/>
+    <x:mergeCell ref="G8:I8"/>
+    <x:mergeCell ref="J5:L5"/>
+    <x:mergeCell ref="J6:L7"/>
+    <x:mergeCell ref="J8:L8"/>
+    <x:mergeCell ref="M5:P5"/>
+    <x:mergeCell ref="M6:P7"/>
+    <x:mergeCell ref="M8:P8"/>
+    <x:mergeCell ref="A10:P10"/>
+    <x:mergeCell ref="A11:E12"/>
+    <x:mergeCell ref="F11:J12"/>
+    <x:mergeCell ref="K11:P12"/>
+    <x:mergeCell ref="A47:P47"/>
+    <x:mergeCell ref="N48:P48"/>
+    <x:mergeCell ref="N49:P57"/>
+    <x:mergeCell ref="A45:P45"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8cbb35c80f475e"/>
 </x:worksheet>
 </file>
 
@@ -13606,7 +16941,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d6ca49ce79046b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ed60b71aef04103"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26376,7 +29711,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd59045c1004405b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e72239bf7a4332"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/outputs/019fcf4b-cafe-75c0-814f-d0b3e093c2ac/trend-meme-stock-cases.xlsx
+++ b/outputs/019fcf4b-cafe-75c0-814f-d0b3e093c2ac/trend-meme-stock-cases.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_안내" sheetId="1" r:id="R2a1c0cdb9f8c45b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_유행이벤트" sheetId="2" r:id="R5de175dda10947f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_종목반응" sheetId="3" r:id="R3c950a999df740f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_출처" sheetId="4" r:id="R19a806caaa15442c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_판정기준" sheetId="5" r:id="Rd7a186bd37664a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_안내" sheetId="1" r:id="Re2d502f7fbcb4b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_유행이벤트" sheetId="2" r:id="Ref70d39a34c046b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_종목반응" sheetId="3" r:id="R7bad23d9b81842f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_출처" sheetId="4" r:id="R406a4931f4284878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_판정기준" sheetId="5" r:id="R781d98d6b5534eb4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +24,7 @@
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
     <x:numFmt numFmtId="204" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="33">
+  <x:fonts count="36">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -217,8 +217,25 @@
       <x:color rgb="FFA65D00"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD81B60"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF5B2942"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF214A9A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="48">
+  <x:fills count="60">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -455,8 +472,68 @@
         <x:fgColor rgb="FFFFF5D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE91E63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF081B4B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214A9A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F0FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE91E63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF081B4B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214A9A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F0FC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="20">
+  <x:borders count="25">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -622,11 +699,69 @@
         <x:color rgb="FFD7DEEC"/>
       </x:right>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF6A7C6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE8D6DF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE8D6DF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE8D6DF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE8D6DF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCAD6EA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCAD6EA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCAD6EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCAD6EA"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="781">
+  <x:cellXfs count="826">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2335,6 +2470,107 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="32" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="48" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="50" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="50" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="50" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="53" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="54" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="54" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="54" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="55" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="56" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="57" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="59" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2469,6 +2705,7 @@
     <c:plotArea>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -2953,7 +3190,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c1b4ec7a44d43d7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R34ee3409b1504f31"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2983,7 +3220,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb476cb21c70844bd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R697a79ac00e74009"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3013,7 +3250,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26224abf435c4ec9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R946134c376fb41a2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3043,7 +3280,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ec5a1962078468f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7817bd7e9ed74bc7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3053,12 +3290,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrendEventsTable" displayName="TrendEventsTable" ref="A5:L303" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TrendEventsTable" displayName="TrendEventsTable" ref="A5:O303" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:O303"/>
+  <x:tableColumns count="15">
     <x:tableColumn id="1" name="이벤트ID"/>
     <x:tableColumn id="2" name="연도"/>
-    <x:tableColumn id="3" name="생활·산업영역"/>
-    <x:tableColumn id="4" name="유형"/>
+    <x:tableColumn id="3" name="대분류"/>
+    <x:tableColumn id="4" name="소분류"/>
     <x:tableColumn id="5" name="유행·트렌드·밈"/>
     <x:tableColumn id="6" name="왜 유행했나"/>
     <x:tableColumn id="7" name="주요 플랫폼·확산권역"/>
@@ -3067,6 +3305,9 @@
     <x:tableColumn id="10" name="연결 종목 수"/>
     <x:tableColumn id="11" name="간단 시간 흐름"/>
     <x:tableColumn id="12" name="출처ID"/>
+    <x:tableColumn id="13" name="주요 관심 연령대(추정)"/>
+    <x:tableColumn id="14" name="성별 관심 경향(추정)"/>
+    <x:tableColumn id="15" name="인구통계 근거 수준"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -4148,9 +4389,9 @@
       <x:c r="O44" s="184"/>
       <x:c r="P44" s="184"/>
     </x:row>
-    <x:row r="45" ht="26" customHeight="1">
+    <x:row r="45" ht="30" customHeight="1">
       <x:c r="A45" s="780" t="str">
-        <x:v>주의: 본 대시보드는 공개 기록 기반 조사 현황입니다. 유행·검색·SNS 확산과 주가 반응의 인과관계를 단정하거나 매수를 권유하지 않습니다.</x:v>
+        <x:v>주의: 유행·검색·SNS 확산과 주가 반응의 인과를 단정하지 않습니다. 연령·성별은 실측 통계가 아니라 사건·플랫폼 성격 기반의 조사용 추정입니다.</x:v>
       </x:c>
       <x:c r="B45" s="780"/>
       <x:c r="C45" s="780"/>
@@ -4875,7 +5116,7 @@
     <x:mergeCell ref="A45:P45"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8cbb35c80f475e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf966b642fe5d44f4"/>
 </x:worksheet>
 </file>
 
@@ -4895,6 +5136,9 @@
     <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="23" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="23" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -4913,9 +5157,9 @@
       <x:c r="K1"/>
       <x:c r="L1"/>
     </x:row>
-    <x:row r="2" ht="25" customHeight="1">
+    <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="130" t="str">
-        <x:v>연도 기준 최신→과거로 정렬했습니다. 같은 연도는 대분류→소분류→사건명 순이며, 정확한 월·일이 확인되지 않은 사건은 임의 날짜를 만들지 않습니다.</x:v>
+        <x:v>연도 기준 최신→과거로 정렬했습니다. 연령대·성별은 실측 통계가 아니라 사건명·소분류·플랫폼 성격을 이용한 조사용 추정이며, 정확한 월·일이 없으면 임의 날짜를 만들지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="130"/>
       <x:c r="C2" s="130"/>
@@ -4966,6 +5210,11 @@
       <x:c r="L3" s="133" t="str">
         <x:v>2009~2026</x:v>
       </x:c>
+      <x:c r="M3" s="818" t="str">
+        <x:v>연령·성별  |  실측 없음·조사용 추정</x:v>
+      </x:c>
+      <x:c r="N3" s="819"/>
+      <x:c r="O3" s="820"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="140" t="str">
@@ -5004,8 +5253,17 @@
       <x:c r="L5" s="140" t="str">
         <x:v>출처ID</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="M5" s="821" t="str">
+        <x:v>주요 관심 연령대(추정)</x:v>
+      </x:c>
+      <x:c r="N5" s="821" t="str">
+        <x:v>성별 관심 경향(추정)</x:v>
+      </x:c>
+      <x:c r="O5" s="821" t="str">
+        <x:v>인구통계 근거 수준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="111" t="str">
         <x:v>TR2026-06</x:v>
       </x:c>
@@ -5044,8 +5302,17 @@
       <x:c r="L6" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="M6" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N6" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O6" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="44" customHeight="1">
       <x:c r="A7" s="111" t="str">
         <x:v>EV0088</x:v>
       </x:c>
@@ -5084,8 +5351,17 @@
       <x:c r="L7" s="111" t="str">
         <x:v>S50;S51;S52</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="M7" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N7" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O7" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="111" t="str">
         <x:v>TR2026-07</x:v>
       </x:c>
@@ -5124,8 +5400,17 @@
       <x:c r="L8" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="M8" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N8" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O8" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="111" t="str">
         <x:v>TR2026-03</x:v>
       </x:c>
@@ -5164,8 +5449,17 @@
       <x:c r="L9" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="M9" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N9" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O9" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="111" t="str">
         <x:v>TR2026-10</x:v>
       </x:c>
@@ -5204,8 +5498,17 @@
       <x:c r="L10" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="M10" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N10" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O10" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="111" t="str">
         <x:v>TR2026-05</x:v>
       </x:c>
@@ -5244,8 +5547,17 @@
       <x:c r="L11" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="M11" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N11" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O11" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="111" t="str">
         <x:v>TR2026-09</x:v>
       </x:c>
@@ -5284,8 +5596,17 @@
       <x:c r="L12" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="M12" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N12" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O12" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="111" t="str">
         <x:v>TR2026-04</x:v>
       </x:c>
@@ -5324,8 +5645,17 @@
       <x:c r="L13" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="M13" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N13" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O13" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="111" t="str">
         <x:v>TR2026-11</x:v>
       </x:c>
@@ -5364,8 +5694,17 @@
       <x:c r="L14" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="M14" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N14" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O14" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="44" customHeight="1">
       <x:c r="A15" s="111" t="str">
         <x:v>TR2026-01</x:v>
       </x:c>
@@ -5404,8 +5743,17 @@
       <x:c r="L15" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="M15" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N15" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O15" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="111" t="str">
         <x:v>TR2026-08</x:v>
       </x:c>
@@ -5444,8 +5792,17 @@
       <x:c r="L16" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="M16" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N16" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O16" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="111" t="str">
         <x:v>TR2026-02</x:v>
       </x:c>
@@ -5484,8 +5841,17 @@
       <x:c r="L17" s="111" t="str">
         <x:v>S241;S242;S243;S244;S245;S246</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="M17" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N17" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O17" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="44" customHeight="1">
       <x:c r="A18" s="111" t="str">
         <x:v>EV0087</x:v>
       </x:c>
@@ -5524,8 +5890,17 @@
       <x:c r="L18" s="111" t="str">
         <x:v>S55</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="M18" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N18" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O18" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="44" customHeight="1">
       <x:c r="A19" s="111" t="str">
         <x:v>EV0083</x:v>
       </x:c>
@@ -5564,8 +5939,17 @@
       <x:c r="L19" s="111" t="str">
         <x:v>S137</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="M19" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N19" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O19" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="111" t="str">
         <x:v>EV0086</x:v>
       </x:c>
@@ -5604,8 +5988,17 @@
       <x:c r="L20" s="111" t="str">
         <x:v>S58</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="M20" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N20" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O20" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="111" t="str">
         <x:v>TR2025-05</x:v>
       </x:c>
@@ -5644,8 +6037,17 @@
       <x:c r="L21" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="M21" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N21" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O21" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="111" t="str">
         <x:v>TR2025-12</x:v>
       </x:c>
@@ -5684,8 +6086,17 @@
       <x:c r="L22" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="M22" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N22" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O22" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="44" customHeight="1">
       <x:c r="A23" s="111" t="str">
         <x:v>TR2025-04</x:v>
       </x:c>
@@ -5724,8 +6135,17 @@
       <x:c r="L23" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="M23" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N23" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O23" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="111" t="str">
         <x:v>TR2025-09</x:v>
       </x:c>
@@ -5764,8 +6184,17 @@
       <x:c r="L24" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="M24" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N24" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O24" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
       <x:c r="A25" s="111" t="str">
         <x:v>TR2025-06</x:v>
       </x:c>
@@ -5804,8 +6233,17 @@
       <x:c r="L25" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="M25" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N25" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O25" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="44" customHeight="1">
       <x:c r="A26" s="111" t="str">
         <x:v>TR2025-07</x:v>
       </x:c>
@@ -5844,8 +6282,17 @@
       <x:c r="L26" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="M26" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N26" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O26" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
       <x:c r="A27" s="111" t="str">
         <x:v>TR2025-10</x:v>
       </x:c>
@@ -5884,8 +6331,17 @@
       <x:c r="L27" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="M27" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N27" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O27" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="44" customHeight="1">
       <x:c r="A28" s="111" t="str">
         <x:v>TR2025-03</x:v>
       </x:c>
@@ -5924,8 +6380,17 @@
       <x:c r="L28" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="M28" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N28" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O28" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="44" customHeight="1">
       <x:c r="A29" s="111" t="str">
         <x:v>TR2025-01</x:v>
       </x:c>
@@ -5964,8 +6429,17 @@
       <x:c r="L29" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="M29" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N29" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O29" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="44" customHeight="1">
       <x:c r="A30" s="111" t="str">
         <x:v>TR2025-02</x:v>
       </x:c>
@@ -6004,8 +6478,17 @@
       <x:c r="L30" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="M30" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N30" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O30" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="44" customHeight="1">
       <x:c r="A31" s="111" t="str">
         <x:v>TR2025-08</x:v>
       </x:c>
@@ -6044,8 +6527,17 @@
       <x:c r="L31" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="M31" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N31" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O31" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="44" customHeight="1">
       <x:c r="A32" s="111" t="str">
         <x:v>TR2025-15</x:v>
       </x:c>
@@ -6084,8 +6576,17 @@
       <x:c r="L32" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="M32" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N32" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O32" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="44" customHeight="1">
       <x:c r="A33" s="111" t="str">
         <x:v>TR2025-13</x:v>
       </x:c>
@@ -6124,8 +6625,17 @@
       <x:c r="L33" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="M33" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N33" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O33" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="44" customHeight="1">
       <x:c r="A34" s="111" t="str">
         <x:v>EV0082</x:v>
       </x:c>
@@ -6164,8 +6674,17 @@
       <x:c r="L34" s="111" t="str">
         <x:v>S64</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="M34" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N34" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O34" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="44" customHeight="1">
       <x:c r="A35" s="111" t="str">
         <x:v>TR2025-14</x:v>
       </x:c>
@@ -6204,8 +6723,17 @@
       <x:c r="L35" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="M35" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N35" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O35" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="44" customHeight="1">
       <x:c r="A36" s="111" t="str">
         <x:v>TR2025-11</x:v>
       </x:c>
@@ -6244,8 +6772,17 @@
       <x:c r="L36" s="111" t="str">
         <x:v>S238;S239;S240</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="M36" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N36" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O36" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="44" customHeight="1">
       <x:c r="A37" s="111" t="str">
         <x:v>TR2024-16</x:v>
       </x:c>
@@ -6284,8 +6821,17 @@
       <x:c r="L37" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="M37" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N37" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O37" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="44" customHeight="1">
       <x:c r="A38" s="111" t="str">
         <x:v>TR2024-04</x:v>
       </x:c>
@@ -6324,8 +6870,17 @@
       <x:c r="L38" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="M38" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N38" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O38" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="44" customHeight="1">
       <x:c r="A39" s="111" t="str">
         <x:v>TR2024-02</x:v>
       </x:c>
@@ -6364,8 +6919,17 @@
       <x:c r="L39" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="M39" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N39" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O39" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="44" customHeight="1">
       <x:c r="A40" s="111" t="str">
         <x:v>TR2024-01</x:v>
       </x:c>
@@ -6404,8 +6968,17 @@
       <x:c r="L40" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="M40" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N40" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O40" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="44" customHeight="1">
       <x:c r="A41" s="111" t="str">
         <x:v>TR2024-03</x:v>
       </x:c>
@@ -6444,8 +7017,17 @@
       <x:c r="L41" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="M41" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N41" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O41" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="44" customHeight="1">
       <x:c r="A42" s="111" t="str">
         <x:v>EV0080</x:v>
       </x:c>
@@ -6484,8 +7066,17 @@
       <x:c r="L42" s="111" t="str">
         <x:v>S117</x:v>
       </x:c>
-    </x:row>
-    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="M42" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N42" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O42" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="44" customHeight="1">
       <x:c r="A43" s="111" t="str">
         <x:v>TR2024-05</x:v>
       </x:c>
@@ -6524,8 +7115,17 @@
       <x:c r="L43" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="M43" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N43" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O43" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="44" customHeight="1">
       <x:c r="A44" s="111" t="str">
         <x:v>EV0075</x:v>
       </x:c>
@@ -6564,8 +7164,17 @@
       <x:c r="L44" s="111" t="str">
         <x:v>S153</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45" ht="42" customHeight="1">
+      <x:c r="M44" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N44" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O44" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="44" customHeight="1">
       <x:c r="A45" s="111" t="str">
         <x:v>TR2024-08</x:v>
       </x:c>
@@ -6604,8 +7213,17 @@
       <x:c r="L45" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" ht="42" customHeight="1">
+      <x:c r="M45" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N45" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O45" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="44" customHeight="1">
       <x:c r="A46" s="111" t="str">
         <x:v>TR2024-06</x:v>
       </x:c>
@@ -6644,8 +7262,17 @@
       <x:c r="L46" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" ht="42" customHeight="1">
+      <x:c r="M46" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N46" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O46" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="44" customHeight="1">
       <x:c r="A47" s="111" t="str">
         <x:v>TR2024-07</x:v>
       </x:c>
@@ -6684,8 +7311,17 @@
       <x:c r="L47" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" ht="42" customHeight="1">
+      <x:c r="M47" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N47" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O47" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="44" customHeight="1">
       <x:c r="A48" s="111" t="str">
         <x:v>EV0076</x:v>
       </x:c>
@@ -6724,8 +7360,17 @@
       <x:c r="L48" s="111" t="str">
         <x:v>S144</x:v>
       </x:c>
-    </x:row>
-    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="M48" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N48" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O48" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="44" customHeight="1">
       <x:c r="A49" s="111" t="str">
         <x:v>TR2024-13</x:v>
       </x:c>
@@ -6764,8 +7409,17 @@
       <x:c r="L49" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="50" ht="42" customHeight="1">
+      <x:c r="M49" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N49" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O49" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="44" customHeight="1">
       <x:c r="A50" s="111" t="str">
         <x:v>EV0073</x:v>
       </x:c>
@@ -6804,8 +7458,17 @@
       <x:c r="L50" s="111" t="str">
         <x:v>S158;S159</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="M50" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N50" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O50" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="44" customHeight="1">
       <x:c r="A51" s="111" t="str">
         <x:v>TR2024-14</x:v>
       </x:c>
@@ -6844,8 +7507,17 @@
       <x:c r="L51" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="52" ht="42" customHeight="1">
+      <x:c r="M51" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N51" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O51" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="44" customHeight="1">
       <x:c r="A52" s="111" t="str">
         <x:v>EV0074</x:v>
       </x:c>
@@ -6884,8 +7556,17 @@
       <x:c r="L52" s="111" t="str">
         <x:v>S143</x:v>
       </x:c>
-    </x:row>
-    <x:row r="53" ht="42" customHeight="1">
+      <x:c r="M52" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N52" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O52" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="44" customHeight="1">
       <x:c r="A53" s="111" t="str">
         <x:v>TR2024-12</x:v>
       </x:c>
@@ -6924,8 +7605,17 @@
       <x:c r="L53" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54" ht="42" customHeight="1">
+      <x:c r="M53" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N53" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O53" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="44" customHeight="1">
       <x:c r="A54" s="111" t="str">
         <x:v>EV0077</x:v>
       </x:c>
@@ -6964,8 +7654,17 @@
       <x:c r="L54" s="111" t="str">
         <x:v>S130;S131</x:v>
       </x:c>
-    </x:row>
-    <x:row r="55" ht="42" customHeight="1">
+      <x:c r="M54" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N54" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O54" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="44" customHeight="1">
       <x:c r="A55" s="111" t="str">
         <x:v>EV0078</x:v>
       </x:c>
@@ -7004,8 +7703,17 @@
       <x:c r="L55" s="111" t="str">
         <x:v>S116</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56" ht="42" customHeight="1">
+      <x:c r="M55" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N55" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O55" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="44" customHeight="1">
       <x:c r="A56" s="111" t="str">
         <x:v>TR2024-10</x:v>
       </x:c>
@@ -7044,8 +7752,17 @@
       <x:c r="L56" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="57" ht="42" customHeight="1">
+      <x:c r="M56" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N56" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O56" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="44" customHeight="1">
       <x:c r="A57" s="111" t="str">
         <x:v>TR2024-09</x:v>
       </x:c>
@@ -7084,8 +7801,17 @@
       <x:c r="L57" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58" ht="42" customHeight="1">
+      <x:c r="M57" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N57" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O57" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="44" customHeight="1">
       <x:c r="A58" s="111" t="str">
         <x:v>TR2024-11</x:v>
       </x:c>
@@ -7124,8 +7850,17 @@
       <x:c r="L58" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59" ht="42" customHeight="1">
+      <x:c r="M58" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N58" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O58" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="44" customHeight="1">
       <x:c r="A59" s="111" t="str">
         <x:v>EV0079</x:v>
       </x:c>
@@ -7164,8 +7899,17 @@
       <x:c r="L59" s="111" t="str">
         <x:v>S65</x:v>
       </x:c>
-    </x:row>
-    <x:row r="60" ht="42" customHeight="1">
+      <x:c r="M59" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N59" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O59" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="44" customHeight="1">
       <x:c r="A60" s="111" t="str">
         <x:v>TR2024-15</x:v>
       </x:c>
@@ -7204,8 +7948,17 @@
       <x:c r="L60" s="111" t="str">
         <x:v>S234;S235;S236;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="M60" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N60" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O60" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="44" customHeight="1">
       <x:c r="A61" s="111" t="str">
         <x:v>TR2023-02</x:v>
       </x:c>
@@ -7244,8 +7997,17 @@
       <x:c r="L61" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="62" ht="42" customHeight="1">
+      <x:c r="M61" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N61" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O61" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="44" customHeight="1">
       <x:c r="A62" s="111" t="str">
         <x:v>TR2023-15</x:v>
       </x:c>
@@ -7284,8 +8046,17 @@
       <x:c r="L62" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="M62" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N62" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O62" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="44" customHeight="1">
       <x:c r="A63" s="111" t="str">
         <x:v>TR2023-04</x:v>
       </x:c>
@@ -7324,8 +8095,17 @@
       <x:c r="L63" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64" ht="42" customHeight="1">
+      <x:c r="M63" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N63" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O63" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="44" customHeight="1">
       <x:c r="A64" s="111" t="str">
         <x:v>TR2023-01</x:v>
       </x:c>
@@ -7364,8 +8144,17 @@
       <x:c r="L64" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="M64" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N64" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O64" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="44" customHeight="1">
       <x:c r="A65" s="111" t="str">
         <x:v>EV0062</x:v>
       </x:c>
@@ -7404,8 +8193,17 @@
       <x:c r="L65" s="111" t="str">
         <x:v>S57</x:v>
       </x:c>
-    </x:row>
-    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="M65" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N65" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O65" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="44" customHeight="1">
       <x:c r="A66" s="111" t="str">
         <x:v>EV0070</x:v>
       </x:c>
@@ -7444,8 +8242,17 @@
       <x:c r="L66" s="111" t="str">
         <x:v>S127</x:v>
       </x:c>
-    </x:row>
-    <x:row r="67" ht="42" customHeight="1">
+      <x:c r="M66" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N66" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O66" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="44" customHeight="1">
       <x:c r="A67" s="111" t="str">
         <x:v>TR2023-05</x:v>
       </x:c>
@@ -7484,8 +8291,17 @@
       <x:c r="L67" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="M67" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N67" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O67" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="44" customHeight="1">
       <x:c r="A68" s="111" t="str">
         <x:v>TR2023-03</x:v>
       </x:c>
@@ -7524,8 +8340,17 @@
       <x:c r="L68" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="M68" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N68" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O68" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="44" customHeight="1">
       <x:c r="A69" s="111" t="str">
         <x:v>EV0059</x:v>
       </x:c>
@@ -7564,8 +8389,17 @@
       <x:c r="L69" s="111" t="str">
         <x:v>S154</x:v>
       </x:c>
-    </x:row>
-    <x:row r="70" ht="42" customHeight="1">
+      <x:c r="M69" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N69" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O69" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="44" customHeight="1">
       <x:c r="A70" s="111" t="str">
         <x:v>TR2023-06</x:v>
       </x:c>
@@ -7604,8 +8438,17 @@
       <x:c r="L70" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="71" ht="42" customHeight="1">
+      <x:c r="M70" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N70" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O70" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="44" customHeight="1">
       <x:c r="A71" s="111" t="str">
         <x:v>TR2023-07</x:v>
       </x:c>
@@ -7644,8 +8487,17 @@
       <x:c r="L71" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="M71" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N71" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O71" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="44" customHeight="1">
       <x:c r="A72" s="111" t="str">
         <x:v>EV0065</x:v>
       </x:c>
@@ -7684,8 +8536,17 @@
       <x:c r="L72" s="111" t="str">
         <x:v>S160</x:v>
       </x:c>
-    </x:row>
-    <x:row r="73" ht="42" customHeight="1">
+      <x:c r="M72" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N72" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O72" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="44" customHeight="1">
       <x:c r="A73" s="111" t="str">
         <x:v>TR2023-10</x:v>
       </x:c>
@@ -7724,8 +8585,17 @@
       <x:c r="L73" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="74" ht="42" customHeight="1">
+      <x:c r="M73" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N73" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O73" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="44" customHeight="1">
       <x:c r="A74" s="111" t="str">
         <x:v>TR2023-09</x:v>
       </x:c>
@@ -7764,8 +8634,17 @@
       <x:c r="L74" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="75" ht="42" customHeight="1">
+      <x:c r="M74" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N74" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O74" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="44" customHeight="1">
       <x:c r="A75" s="111" t="str">
         <x:v>TR2023-14</x:v>
       </x:c>
@@ -7804,8 +8683,17 @@
       <x:c r="L75" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="76" ht="42" customHeight="1">
+      <x:c r="M75" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N75" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O75" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="44" customHeight="1">
       <x:c r="A76" s="111" t="str">
         <x:v>EV0063</x:v>
       </x:c>
@@ -7844,8 +8732,17 @@
       <x:c r="L76" s="111" t="str">
         <x:v>S141;S142</x:v>
       </x:c>
-    </x:row>
-    <x:row r="77" ht="42" customHeight="1">
+      <x:c r="M76" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N76" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O76" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="44" customHeight="1">
       <x:c r="A77" s="111" t="str">
         <x:v>EV0066</x:v>
       </x:c>
@@ -7884,8 +8781,17 @@
       <x:c r="L77" s="111" t="str">
         <x:v>S60</x:v>
       </x:c>
-    </x:row>
-    <x:row r="78" ht="42" customHeight="1">
+      <x:c r="M77" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N77" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O77" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="44" customHeight="1">
       <x:c r="A78" s="111" t="str">
         <x:v>EV0067</x:v>
       </x:c>
@@ -7924,8 +8830,17 @@
       <x:c r="L78" s="111" t="str">
         <x:v>S115</x:v>
       </x:c>
-    </x:row>
-    <x:row r="79" ht="42" customHeight="1">
+      <x:c r="M78" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N78" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O78" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="44" customHeight="1">
       <x:c r="A79" s="111" t="str">
         <x:v>TR2023-12</x:v>
       </x:c>
@@ -7964,8 +8879,17 @@
       <x:c r="L79" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="80" ht="42" customHeight="1">
+      <x:c r="M79" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N79" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O79" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="44" customHeight="1">
       <x:c r="A80" s="111" t="str">
         <x:v>TR2023-11</x:v>
       </x:c>
@@ -8004,8 +8928,17 @@
       <x:c r="L80" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="81" ht="42" customHeight="1">
+      <x:c r="M80" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N80" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O80" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="44" customHeight="1">
       <x:c r="A81" s="111" t="str">
         <x:v>EV0071</x:v>
       </x:c>
@@ -8044,8 +8977,17 @@
       <x:c r="L81" s="111" t="str">
         <x:v>S119;S120;S121;S122</x:v>
       </x:c>
-    </x:row>
-    <x:row r="82" ht="42" customHeight="1">
+      <x:c r="M81" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N81" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O81" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="44" customHeight="1">
       <x:c r="A82" s="111" t="str">
         <x:v>TR2023-08</x:v>
       </x:c>
@@ -8084,8 +9026,17 @@
       <x:c r="L82" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="83" ht="42" customHeight="1">
+      <x:c r="M82" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N82" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O82" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="44" customHeight="1">
       <x:c r="A83" s="111" t="str">
         <x:v>EV0060</x:v>
       </x:c>
@@ -8124,8 +9075,17 @@
       <x:c r="L83" s="111" t="str">
         <x:v>S56</x:v>
       </x:c>
-    </x:row>
-    <x:row r="84" ht="42" customHeight="1">
+      <x:c r="M83" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N83" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O83" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="44" customHeight="1">
       <x:c r="A84" s="111" t="str">
         <x:v>TR2023-13</x:v>
       </x:c>
@@ -8164,8 +9124,17 @@
       <x:c r="L84" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="85" ht="42" customHeight="1">
+      <x:c r="M84" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N84" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O84" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="44" customHeight="1">
       <x:c r="A85" s="111" t="str">
         <x:v>EV0064</x:v>
       </x:c>
@@ -8204,8 +9173,17 @@
       <x:c r="L85" s="111" t="str">
         <x:v>S124</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86" ht="42" customHeight="1">
+      <x:c r="M85" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N85" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O85" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="44" customHeight="1">
       <x:c r="A86" s="111" t="str">
         <x:v>EV0061</x:v>
       </x:c>
@@ -8244,8 +9222,17 @@
       <x:c r="L86" s="111" t="str">
         <x:v>S123</x:v>
       </x:c>
-    </x:row>
-    <x:row r="87" ht="42" customHeight="1">
+      <x:c r="M86" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N86" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O86" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="44" customHeight="1">
       <x:c r="A87" s="111" t="str">
         <x:v>TR2023-16</x:v>
       </x:c>
@@ -8284,8 +9271,17 @@
       <x:c r="L87" s="111" t="str">
         <x:v>S232;S233;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88" ht="42" customHeight="1">
+      <x:c r="M87" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N87" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O87" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="44" customHeight="1">
       <x:c r="A88" s="111" t="str">
         <x:v>TR2022-02</x:v>
       </x:c>
@@ -8324,8 +9320,17 @@
       <x:c r="L88" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="89" ht="42" customHeight="1">
+      <x:c r="M88" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N88" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O88" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="44" customHeight="1">
       <x:c r="A89" s="111" t="str">
         <x:v>EV0051</x:v>
       </x:c>
@@ -8364,8 +9369,17 @@
       <x:c r="L89" s="111" t="str">
         <x:v>S113</x:v>
       </x:c>
-    </x:row>
-    <x:row r="90" ht="42" customHeight="1">
+      <x:c r="M89" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N89" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O89" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="44" customHeight="1">
       <x:c r="A90" s="111" t="str">
         <x:v>TR2022-01</x:v>
       </x:c>
@@ -8404,8 +9418,17 @@
       <x:c r="L90" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="91" ht="42" customHeight="1">
+      <x:c r="M90" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N90" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O90" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="44" customHeight="1">
       <x:c r="A91" s="111" t="str">
         <x:v>EV0054</x:v>
       </x:c>
@@ -8444,8 +9467,17 @@
       <x:c r="L91" s="111" t="str">
         <x:v>S54</x:v>
       </x:c>
-    </x:row>
-    <x:row r="92" ht="42" customHeight="1">
+      <x:c r="M91" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N91" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O91" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="44" customHeight="1">
       <x:c r="A92" s="111" t="str">
         <x:v>EV0057</x:v>
       </x:c>
@@ -8484,8 +9516,17 @@
       <x:c r="L92" s="111" t="str">
         <x:v>S134</x:v>
       </x:c>
-    </x:row>
-    <x:row r="93" ht="42" customHeight="1">
+      <x:c r="M92" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N92" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O92" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="44" customHeight="1">
       <x:c r="A93" s="111" t="str">
         <x:v>EV0053</x:v>
       </x:c>
@@ -8524,8 +9565,17 @@
       <x:c r="L93" s="111" t="str">
         <x:v>S114</x:v>
       </x:c>
-    </x:row>
-    <x:row r="94" ht="42" customHeight="1">
+      <x:c r="M93" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N93" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O93" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="44" customHeight="1">
       <x:c r="A94" s="111" t="str">
         <x:v>TR2022-06</x:v>
       </x:c>
@@ -8564,8 +9614,17 @@
       <x:c r="L94" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="95" ht="42" customHeight="1">
+      <x:c r="M94" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N94" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O94" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="44" customHeight="1">
       <x:c r="A95" s="111" t="str">
         <x:v>EV0050</x:v>
       </x:c>
@@ -8604,8 +9663,17 @@
       <x:c r="L95" s="111" t="str">
         <x:v>S112</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="42" customHeight="1">
+      <x:c r="M95" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N95" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O95" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="44" customHeight="1">
       <x:c r="A96" s="111" t="str">
         <x:v>TR2022-07</x:v>
       </x:c>
@@ -8644,8 +9712,17 @@
       <x:c r="L96" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="97" ht="42" customHeight="1">
+      <x:c r="M96" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N96" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O96" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="44" customHeight="1">
       <x:c r="A97" s="111" t="str">
         <x:v>TR2022-10</x:v>
       </x:c>
@@ -8684,8 +9761,17 @@
       <x:c r="L97" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="98" ht="42" customHeight="1">
+      <x:c r="M97" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N97" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O97" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="44" customHeight="1">
       <x:c r="A98" s="111" t="str">
         <x:v>TR2022-04</x:v>
       </x:c>
@@ -8724,8 +9810,17 @@
       <x:c r="L98" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="99" ht="42" customHeight="1">
+      <x:c r="M98" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N98" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O98" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="44" customHeight="1">
       <x:c r="A99" s="111" t="str">
         <x:v>TR2022-09</x:v>
       </x:c>
@@ -8764,8 +9859,17 @@
       <x:c r="L99" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="100" ht="42" customHeight="1">
+      <x:c r="M99" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N99" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O99" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="44" customHeight="1">
       <x:c r="A100" s="111" t="str">
         <x:v>EV0055</x:v>
       </x:c>
@@ -8804,8 +9908,17 @@
       <x:c r="L100" s="111" t="str">
         <x:v>S138</x:v>
       </x:c>
-    </x:row>
-    <x:row r="101" ht="42" customHeight="1">
+      <x:c r="M100" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N100" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O100" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="44" customHeight="1">
       <x:c r="A101" s="111" t="str">
         <x:v>EV0056</x:v>
       </x:c>
@@ -8844,8 +9957,17 @@
       <x:c r="L101" s="111" t="str">
         <x:v>S139</x:v>
       </x:c>
-    </x:row>
-    <x:row r="102" ht="42" customHeight="1">
+      <x:c r="M101" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N101" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O101" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="44" customHeight="1">
       <x:c r="A102" s="111" t="str">
         <x:v>EV0052</x:v>
       </x:c>
@@ -8884,8 +10006,17 @@
       <x:c r="L102" s="111" t="str">
         <x:v>S114</x:v>
       </x:c>
-    </x:row>
-    <x:row r="103" ht="42" customHeight="1">
+      <x:c r="M102" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N102" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O102" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="44" customHeight="1">
       <x:c r="A103" s="111" t="str">
         <x:v>TR2022-13</x:v>
       </x:c>
@@ -8924,8 +10055,17 @@
       <x:c r="L103" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="104" ht="42" customHeight="1">
+      <x:c r="M103" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N103" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O103" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="44" customHeight="1">
       <x:c r="A104" s="111" t="str">
         <x:v>TR2022-08</x:v>
       </x:c>
@@ -8964,8 +10104,17 @@
       <x:c r="L104" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="105" ht="42" customHeight="1">
+      <x:c r="M104" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N104" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O104" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="44" customHeight="1">
       <x:c r="A105" s="111" t="str">
         <x:v>EV0049</x:v>
       </x:c>
@@ -9004,8 +10153,17 @@
       <x:c r="L105" s="111" t="str">
         <x:v>S128;S129</x:v>
       </x:c>
-    </x:row>
-    <x:row r="106" ht="42" customHeight="1">
+      <x:c r="M105" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N105" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O105" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="44" customHeight="1">
       <x:c r="A106" s="111" t="str">
         <x:v>TR2022-03</x:v>
       </x:c>
@@ -9044,8 +10202,17 @@
       <x:c r="L106" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="107" ht="42" customHeight="1">
+      <x:c r="M106" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N106" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O106" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="44" customHeight="1">
       <x:c r="A107" s="111" t="str">
         <x:v>TR2022-14</x:v>
       </x:c>
@@ -9084,8 +10251,17 @@
       <x:c r="L107" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="108" ht="42" customHeight="1">
+      <x:c r="M107" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N107" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O107" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="44" customHeight="1">
       <x:c r="A108" s="111" t="str">
         <x:v>TR2022-12</x:v>
       </x:c>
@@ -9124,8 +10300,17 @@
       <x:c r="L108" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="109" ht="42" customHeight="1">
+      <x:c r="M108" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N108" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O108" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="44" customHeight="1">
       <x:c r="A109" s="111" t="str">
         <x:v>TR2022-05</x:v>
       </x:c>
@@ -9164,8 +10349,17 @@
       <x:c r="L109" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="110" ht="42" customHeight="1">
+      <x:c r="M109" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N109" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O109" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="44" customHeight="1">
       <x:c r="A110" s="111" t="str">
         <x:v>TR2022-11</x:v>
       </x:c>
@@ -9204,8 +10398,17 @@
       <x:c r="L110" s="111" t="str">
         <x:v>S230;S231;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="111" ht="42" customHeight="1">
+      <x:c r="M110" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N110" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O110" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="44" customHeight="1">
       <x:c r="A111" s="111" t="str">
         <x:v>TR2021-05</x:v>
       </x:c>
@@ -9244,8 +10447,17 @@
       <x:c r="L111" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="112" ht="42" customHeight="1">
+      <x:c r="M111" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N111" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O111" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="44" customHeight="1">
       <x:c r="A112" s="111" t="str">
         <x:v>TR2021-11</x:v>
       </x:c>
@@ -9284,8 +10496,17 @@
       <x:c r="L112" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="113" ht="42" customHeight="1">
+      <x:c r="M112" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N112" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O112" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="44" customHeight="1">
       <x:c r="A113" s="111" t="str">
         <x:v>TR2021-01</x:v>
       </x:c>
@@ -9324,8 +10545,17 @@
       <x:c r="L113" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="114" ht="42" customHeight="1">
+      <x:c r="M113" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N113" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O113" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="44" customHeight="1">
       <x:c r="A114" s="111" t="str">
         <x:v>EV0043</x:v>
       </x:c>
@@ -9364,8 +10594,17 @@
       <x:c r="L114" s="111" t="str">
         <x:v>S135;S136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="115" ht="42" customHeight="1">
+      <x:c r="M114" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N114" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O114" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="44" customHeight="1">
       <x:c r="A115" s="111" t="str">
         <x:v>EV0047</x:v>
       </x:c>
@@ -9404,8 +10643,17 @@
       <x:c r="L115" s="111" t="str">
         <x:v>S155</x:v>
       </x:c>
-    </x:row>
-    <x:row r="116" ht="42" customHeight="1">
+      <x:c r="M115" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N115" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O115" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="44" customHeight="1">
       <x:c r="A116" s="111" t="str">
         <x:v>TR2021-13</x:v>
       </x:c>
@@ -9444,8 +10692,17 @@
       <x:c r="L116" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="117" ht="42" customHeight="1">
+      <x:c r="M116" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N116" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O116" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="44" customHeight="1">
       <x:c r="A117" s="111" t="str">
         <x:v>TR2021-08</x:v>
       </x:c>
@@ -9484,8 +10741,17 @@
       <x:c r="L117" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="118" ht="42" customHeight="1">
+      <x:c r="M117" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N117" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O117" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="44" customHeight="1">
       <x:c r="A118" s="111" t="str">
         <x:v>TR2021-02</x:v>
       </x:c>
@@ -9524,8 +10790,17 @@
       <x:c r="L118" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="119" ht="42" customHeight="1">
+      <x:c r="M118" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N118" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O118" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="44" customHeight="1">
       <x:c r="A119" s="111" t="str">
         <x:v>TR2021-04</x:v>
       </x:c>
@@ -9564,8 +10839,17 @@
       <x:c r="L119" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="120" ht="42" customHeight="1">
+      <x:c r="M119" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N119" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O119" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="44" customHeight="1">
       <x:c r="A120" s="111" t="str">
         <x:v>EV0041</x:v>
       </x:c>
@@ -9604,8 +10888,17 @@
       <x:c r="L120" s="111" t="str">
         <x:v>S110;S111</x:v>
       </x:c>
-    </x:row>
-    <x:row r="121" ht="42" customHeight="1">
+      <x:c r="M120" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N120" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O120" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="44" customHeight="1">
       <x:c r="A121" s="111" t="str">
         <x:v>EV0042</x:v>
       </x:c>
@@ -9644,8 +10937,17 @@
       <x:c r="L121" s="111" t="str">
         <x:v>S110;S111</x:v>
       </x:c>
-    </x:row>
-    <x:row r="122" ht="42" customHeight="1">
+      <x:c r="M121" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N121" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O121" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="44" customHeight="1">
       <x:c r="A122" s="111" t="str">
         <x:v>TR2021-10</x:v>
       </x:c>
@@ -9684,8 +10986,17 @@
       <x:c r="L122" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="123" ht="42" customHeight="1">
+      <x:c r="M122" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N122" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O122" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="44" customHeight="1">
       <x:c r="A123" s="111" t="str">
         <x:v>TR2021-07</x:v>
       </x:c>
@@ -9724,8 +11035,17 @@
       <x:c r="L123" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="124" ht="42" customHeight="1">
+      <x:c r="M123" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N123" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O123" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="44" customHeight="1">
       <x:c r="A124" s="111" t="str">
         <x:v>TR2021-06</x:v>
       </x:c>
@@ -9764,8 +11084,17 @@
       <x:c r="L124" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="125" ht="42" customHeight="1">
+      <x:c r="M124" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N124" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O124" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="44" customHeight="1">
       <x:c r="A125" s="111" t="str">
         <x:v>TR2021-09</x:v>
       </x:c>
@@ -9804,8 +11133,17 @@
       <x:c r="L125" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="126" ht="42" customHeight="1">
+      <x:c r="M125" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N125" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O125" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="44" customHeight="1">
       <x:c r="A126" s="111" t="str">
         <x:v>TR2021-03</x:v>
       </x:c>
@@ -9844,8 +11182,17 @@
       <x:c r="L126" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="127" ht="42" customHeight="1">
+      <x:c r="M126" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N126" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O126" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="44" customHeight="1">
       <x:c r="A127" s="111" t="str">
         <x:v>EV0045</x:v>
       </x:c>
@@ -9884,8 +11231,17 @@
       <x:c r="L127" s="111" t="str">
         <x:v>S33;S34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="128" ht="42" customHeight="1">
+      <x:c r="M127" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N127" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O127" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="44" customHeight="1">
       <x:c r="A128" s="111" t="str">
         <x:v>EV0048</x:v>
       </x:c>
@@ -9924,8 +11280,17 @@
       <x:c r="L128" s="111" t="str">
         <x:v>S132;S133</x:v>
       </x:c>
-    </x:row>
-    <x:row r="129" ht="42" customHeight="1">
+      <x:c r="M128" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N128" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O128" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="44" customHeight="1">
       <x:c r="A129" s="111" t="str">
         <x:v>TR2021-14</x:v>
       </x:c>
@@ -9964,8 +11329,17 @@
       <x:c r="L129" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="130" ht="42" customHeight="1">
+      <x:c r="M129" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N129" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O129" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="44" customHeight="1">
       <x:c r="A130" s="111" t="str">
         <x:v>TR2021-12</x:v>
       </x:c>
@@ -10004,8 +11378,17 @@
       <x:c r="L130" s="111" t="str">
         <x:v>S228;S229;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="131" ht="42" customHeight="1">
+      <x:c r="M130" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N130" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O130" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="44" customHeight="1">
       <x:c r="A131" s="111" t="str">
         <x:v>EV0040</x:v>
       </x:c>
@@ -10044,8 +11427,17 @@
       <x:c r="L131" s="111" t="str">
         <x:v>S151;S152</x:v>
       </x:c>
-    </x:row>
-    <x:row r="132" ht="42" customHeight="1">
+      <x:c r="M131" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N131" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O131" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="44" customHeight="1">
       <x:c r="A132" s="111" t="str">
         <x:v>EV0044</x:v>
       </x:c>
@@ -10084,8 +11476,17 @@
       <x:c r="L132" s="111" t="str">
         <x:v>S149;S150</x:v>
       </x:c>
-    </x:row>
-    <x:row r="133" ht="42" customHeight="1">
+      <x:c r="M132" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N132" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O132" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="44" customHeight="1">
       <x:c r="A133" s="111" t="str">
         <x:v>TR2020-11</x:v>
       </x:c>
@@ -10124,8 +11525,17 @@
       <x:c r="L133" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="134" ht="42" customHeight="1">
+      <x:c r="M133" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N133" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O133" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="44" customHeight="1">
       <x:c r="A134" s="111" t="str">
         <x:v>EV0035</x:v>
       </x:c>
@@ -10164,8 +11574,17 @@
       <x:c r="L134" s="111" t="str">
         <x:v>S61</x:v>
       </x:c>
-    </x:row>
-    <x:row r="135" ht="42" customHeight="1">
+      <x:c r="M134" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N134" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O134" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="44" customHeight="1">
       <x:c r="A135" s="111" t="str">
         <x:v>TR2020-09</x:v>
       </x:c>
@@ -10204,8 +11623,17 @@
       <x:c r="L135" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="136" ht="42" customHeight="1">
+      <x:c r="M135" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N135" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O135" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="44" customHeight="1">
       <x:c r="A136" s="111" t="str">
         <x:v>TR2020-05</x:v>
       </x:c>
@@ -10244,8 +11672,17 @@
       <x:c r="L136" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="137" ht="42" customHeight="1">
+      <x:c r="M136" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N136" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O136" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="44" customHeight="1">
       <x:c r="A137" s="111" t="str">
         <x:v>EV0034</x:v>
       </x:c>
@@ -10284,8 +11721,17 @@
       <x:c r="L137" s="111" t="str">
         <x:v>S35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="138" ht="42" customHeight="1">
+      <x:c r="M137" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N137" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O137" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="44" customHeight="1">
       <x:c r="A138" s="111" t="str">
         <x:v>TR2020-04</x:v>
       </x:c>
@@ -10324,8 +11770,17 @@
       <x:c r="L138" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="139" ht="42" customHeight="1">
+      <x:c r="M138" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N138" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O138" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="44" customHeight="1">
       <x:c r="A139" s="111" t="str">
         <x:v>TR2020-01</x:v>
       </x:c>
@@ -10364,8 +11819,17 @@
       <x:c r="L139" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="140" ht="42" customHeight="1">
+      <x:c r="M139" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N139" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O139" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="44" customHeight="1">
       <x:c r="A140" s="111" t="str">
         <x:v>EV0036</x:v>
       </x:c>
@@ -10404,8 +11868,17 @@
       <x:c r="L140" s="111" t="str">
         <x:v>S59</x:v>
       </x:c>
-    </x:row>
-    <x:row r="141" ht="42" customHeight="1">
+      <x:c r="M140" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N140" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O140" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="44" customHeight="1">
       <x:c r="A141" s="111" t="str">
         <x:v>TR2020-08</x:v>
       </x:c>
@@ -10444,8 +11917,17 @@
       <x:c r="L141" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="142" ht="42" customHeight="1">
+      <x:c r="M141" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N141" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O141" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="44" customHeight="1">
       <x:c r="A142" s="111" t="str">
         <x:v>TR2020-07</x:v>
       </x:c>
@@ -10484,8 +11966,17 @@
       <x:c r="L142" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="143" ht="42" customHeight="1">
+      <x:c r="M142" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N142" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O142" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="44" customHeight="1">
       <x:c r="A143" s="111" t="str">
         <x:v>TR2020-12</x:v>
       </x:c>
@@ -10524,8 +12015,17 @@
       <x:c r="L143" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="144" ht="42" customHeight="1">
+      <x:c r="M143" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N143" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O143" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="44" customHeight="1">
       <x:c r="A144" s="111" t="str">
         <x:v>TR2020-15</x:v>
       </x:c>
@@ -10564,8 +12064,17 @@
       <x:c r="L144" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="145" ht="42" customHeight="1">
+      <x:c r="M144" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N144" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O144" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="44" customHeight="1">
       <x:c r="A145" s="111" t="str">
         <x:v>TR2020-02</x:v>
       </x:c>
@@ -10604,8 +12113,17 @@
       <x:c r="L145" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="146" ht="42" customHeight="1">
+      <x:c r="M145" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N145" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O145" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="44" customHeight="1">
       <x:c r="A146" s="111" t="str">
         <x:v>TR2020-14</x:v>
       </x:c>
@@ -10644,8 +12162,17 @@
       <x:c r="L146" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="147" ht="42" customHeight="1">
+      <x:c r="M146" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N146" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O146" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="44" customHeight="1">
       <x:c r="A147" s="111" t="str">
         <x:v>TR2020-13</x:v>
       </x:c>
@@ -10684,8 +12211,17 @@
       <x:c r="L147" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="148" ht="42" customHeight="1">
+      <x:c r="M147" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N147" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O147" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="44" customHeight="1">
       <x:c r="A148" s="111" t="str">
         <x:v>TR2020-03</x:v>
       </x:c>
@@ -10724,8 +12260,17 @@
       <x:c r="L148" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="149" ht="42" customHeight="1">
+      <x:c r="M148" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N148" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O148" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="44" customHeight="1">
       <x:c r="A149" s="111" t="str">
         <x:v>EV0037</x:v>
       </x:c>
@@ -10764,8 +12309,17 @@
       <x:c r="L149" s="111" t="str">
         <x:v>S109</x:v>
       </x:c>
-    </x:row>
-    <x:row r="150" ht="42" customHeight="1">
+      <x:c r="M149" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N149" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O149" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="44" customHeight="1">
       <x:c r="A150" s="111" t="str">
         <x:v>EV0038</x:v>
       </x:c>
@@ -10804,8 +12358,17 @@
       <x:c r="L150" s="111" t="str">
         <x:v>S109</x:v>
       </x:c>
-    </x:row>
-    <x:row r="151" ht="42" customHeight="1">
+      <x:c r="M150" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N150" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O150" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="44" customHeight="1">
       <x:c r="A151" s="111" t="str">
         <x:v>EV0039</x:v>
       </x:c>
@@ -10844,8 +12407,17 @@
       <x:c r="L151" s="111" t="str">
         <x:v>S108</x:v>
       </x:c>
-    </x:row>
-    <x:row r="152" ht="42" customHeight="1">
+      <x:c r="M151" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N151" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O151" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="44" customHeight="1">
       <x:c r="A152" s="111" t="str">
         <x:v>TR2020-06</x:v>
       </x:c>
@@ -10884,8 +12456,17 @@
       <x:c r="L152" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="153" ht="42" customHeight="1">
+      <x:c r="M152" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N152" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O152" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="44" customHeight="1">
       <x:c r="A153" s="111" t="str">
         <x:v>TR2020-10</x:v>
       </x:c>
@@ -10924,8 +12505,17 @@
       <x:c r="L153" s="111" t="str">
         <x:v>S226;S227;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="154" ht="42" customHeight="1">
+      <x:c r="M153" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N153" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O153" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="44" customHeight="1">
       <x:c r="A154" s="111" t="str">
         <x:v>EV0032</x:v>
       </x:c>
@@ -10964,8 +12554,17 @@
       <x:c r="L154" s="111" t="str">
         <x:v>S125;S126</x:v>
       </x:c>
-    </x:row>
-    <x:row r="155" ht="42" customHeight="1">
+      <x:c r="M154" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N154" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O154" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="44" customHeight="1">
       <x:c r="A155" s="111" t="str">
         <x:v>TR2019-09</x:v>
       </x:c>
@@ -11004,8 +12603,17 @@
       <x:c r="L155" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="156" ht="42" customHeight="1">
+      <x:c r="M155" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N155" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O155" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="44" customHeight="1">
       <x:c r="A156" s="111" t="str">
         <x:v>TR2019-08</x:v>
       </x:c>
@@ -11044,8 +12652,17 @@
       <x:c r="L156" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="157" ht="42" customHeight="1">
+      <x:c r="M156" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N156" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O156" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="44" customHeight="1">
       <x:c r="A157" s="111" t="str">
         <x:v>EV0029</x:v>
       </x:c>
@@ -11084,8 +12701,17 @@
       <x:c r="L157" s="111" t="str">
         <x:v>S148</x:v>
       </x:c>
-    </x:row>
-    <x:row r="158" ht="42" customHeight="1">
+      <x:c r="M157" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N157" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O157" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="44" customHeight="1">
       <x:c r="A158" s="111" t="str">
         <x:v>TR2019-11</x:v>
       </x:c>
@@ -11124,8 +12750,17 @@
       <x:c r="L158" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="159" ht="42" customHeight="1">
+      <x:c r="M158" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N158" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O158" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="44" customHeight="1">
       <x:c r="A159" s="111" t="str">
         <x:v>TR2019-07</x:v>
       </x:c>
@@ -11164,8 +12799,17 @@
       <x:c r="L159" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="160" ht="42" customHeight="1">
+      <x:c r="M159" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N159" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O159" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="44" customHeight="1">
       <x:c r="A160" s="111" t="str">
         <x:v>TR2019-13</x:v>
       </x:c>
@@ -11204,8 +12848,17 @@
       <x:c r="L160" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="161" ht="42" customHeight="1">
+      <x:c r="M160" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N160" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O160" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="44" customHeight="1">
       <x:c r="A161" s="111" t="str">
         <x:v>TR2019-03</x:v>
       </x:c>
@@ -11244,8 +12897,17 @@
       <x:c r="L161" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="162" ht="42" customHeight="1">
+      <x:c r="M161" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N161" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O161" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="44" customHeight="1">
       <x:c r="A162" s="111" t="str">
         <x:v>TR2019-01</x:v>
       </x:c>
@@ -11284,8 +12946,17 @@
       <x:c r="L162" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="163" ht="42" customHeight="1">
+      <x:c r="M162" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N162" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O162" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="44" customHeight="1">
       <x:c r="A163" s="111" t="str">
         <x:v>TR2019-04</x:v>
       </x:c>
@@ -11324,8 +12995,17 @@
       <x:c r="L163" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="164" ht="42" customHeight="1">
+      <x:c r="M163" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N163" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O163" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="44" customHeight="1">
       <x:c r="A164" s="111" t="str">
         <x:v>EV0025</x:v>
       </x:c>
@@ -11364,8 +13044,17 @@
       <x:c r="L164" s="111" t="str">
         <x:v>S161</x:v>
       </x:c>
-    </x:row>
-    <x:row r="165" ht="42" customHeight="1">
+      <x:c r="M164" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N164" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O164" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="44" customHeight="1">
       <x:c r="A165" s="111" t="str">
         <x:v>TR2019-02</x:v>
       </x:c>
@@ -11404,8 +13093,17 @@
       <x:c r="L165" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="166" ht="42" customHeight="1">
+      <x:c r="M165" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N165" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O165" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="44" customHeight="1">
       <x:c r="A166" s="111" t="str">
         <x:v>TR2019-06</x:v>
       </x:c>
@@ -11444,8 +13142,17 @@
       <x:c r="L166" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="167" ht="42" customHeight="1">
+      <x:c r="M166" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N166" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O166" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="44" customHeight="1">
       <x:c r="A167" s="111" t="str">
         <x:v>TR2019-05</x:v>
       </x:c>
@@ -11484,8 +13191,17 @@
       <x:c r="L167" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="168" ht="42" customHeight="1">
+      <x:c r="M167" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N167" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O167" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="44" customHeight="1">
       <x:c r="A168" s="111" t="str">
         <x:v>TR2019-10</x:v>
       </x:c>
@@ -11524,8 +13240,17 @@
       <x:c r="L168" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="169" ht="42" customHeight="1">
+      <x:c r="M168" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N168" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O168" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="44" customHeight="1">
       <x:c r="A169" s="111" t="str">
         <x:v>TR2019-12</x:v>
       </x:c>
@@ -11564,8 +13289,17 @@
       <x:c r="L169" s="111" t="str">
         <x:v>S225;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="170" ht="42" customHeight="1">
+      <x:c r="M169" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N169" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O169" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="44" customHeight="1">
       <x:c r="A170" s="111" t="str">
         <x:v>EV0026</x:v>
       </x:c>
@@ -11604,8 +13338,17 @@
       <x:c r="L170" s="111" t="str">
         <x:v>S106</x:v>
       </x:c>
-    </x:row>
-    <x:row r="171" ht="42" customHeight="1">
+      <x:c r="M170" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N170" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O170" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="44" customHeight="1">
       <x:c r="A171" s="111" t="str">
         <x:v>EV0027</x:v>
       </x:c>
@@ -11644,8 +13387,17 @@
       <x:c r="L171" s="111" t="str">
         <x:v>S106</x:v>
       </x:c>
-    </x:row>
-    <x:row r="172" ht="42" customHeight="1">
+      <x:c r="M171" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N171" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O171" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="44" customHeight="1">
       <x:c r="A172" s="111" t="str">
         <x:v>EV0030</x:v>
       </x:c>
@@ -11684,8 +13436,17 @@
       <x:c r="L172" s="111" t="str">
         <x:v>S107</x:v>
       </x:c>
-    </x:row>
-    <x:row r="173" ht="42" customHeight="1">
+      <x:c r="M172" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N172" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O172" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="44" customHeight="1">
       <x:c r="A173" s="111" t="str">
         <x:v>EV0028</x:v>
       </x:c>
@@ -11724,8 +13485,17 @@
       <x:c r="L173" s="111" t="str">
         <x:v>S140</x:v>
       </x:c>
-    </x:row>
-    <x:row r="174" ht="42" customHeight="1">
+      <x:c r="M173" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N173" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O173" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="44" customHeight="1">
       <x:c r="A174" s="111" t="str">
         <x:v>TR2018-08</x:v>
       </x:c>
@@ -11764,8 +13534,17 @@
       <x:c r="L174" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="175" ht="42" customHeight="1">
+      <x:c r="M174" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N174" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O174" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="44" customHeight="1">
       <x:c r="A175" s="111" t="str">
         <x:v>TR2018-09</x:v>
       </x:c>
@@ -11804,8 +13583,17 @@
       <x:c r="L175" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="176" ht="42" customHeight="1">
+      <x:c r="M175" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N175" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O175" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="44" customHeight="1">
       <x:c r="A176" s="111" t="str">
         <x:v>TR2018-04</x:v>
       </x:c>
@@ -11844,8 +13632,17 @@
       <x:c r="L176" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="177" ht="42" customHeight="1">
+      <x:c r="M176" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N176" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O176" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="44" customHeight="1">
       <x:c r="A177" s="111" t="str">
         <x:v>TR2018-03</x:v>
       </x:c>
@@ -11884,8 +13681,17 @@
       <x:c r="L177" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="178" ht="42" customHeight="1">
+      <x:c r="M177" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N177" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O177" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="44" customHeight="1">
       <x:c r="A178" s="111" t="str">
         <x:v>TR2018-02</x:v>
       </x:c>
@@ -11924,8 +13730,17 @@
       <x:c r="L178" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="179" ht="42" customHeight="1">
+      <x:c r="M178" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N178" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O178" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="44" customHeight="1">
       <x:c r="A179" s="111" t="str">
         <x:v>TR2018-01</x:v>
       </x:c>
@@ -11964,8 +13779,17 @@
       <x:c r="L179" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="180" ht="42" customHeight="1">
+      <x:c r="M179" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N179" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O179" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="44" customHeight="1">
       <x:c r="A180" s="111" t="str">
         <x:v>TR2018-05</x:v>
       </x:c>
@@ -12004,8 +13828,17 @@
       <x:c r="L180" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="181" ht="42" customHeight="1">
+      <x:c r="M180" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N180" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O180" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="44" customHeight="1">
       <x:c r="A181" s="111" t="str">
         <x:v>TR2018-06</x:v>
       </x:c>
@@ -12044,8 +13877,17 @@
       <x:c r="L181" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="182" ht="42" customHeight="1">
+      <x:c r="M181" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N181" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O181" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="44" customHeight="1">
       <x:c r="A182" s="111" t="str">
         <x:v>TR2018-14</x:v>
       </x:c>
@@ -12084,8 +13926,17 @@
       <x:c r="L182" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="183" ht="42" customHeight="1">
+      <x:c r="M182" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N182" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O182" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="44" customHeight="1">
       <x:c r="A183" s="111" t="str">
         <x:v>TR2018-07</x:v>
       </x:c>
@@ -12124,8 +13975,17 @@
       <x:c r="L183" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="184" ht="42" customHeight="1">
+      <x:c r="M183" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N183" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O183" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="44" customHeight="1">
       <x:c r="A184" s="111" t="str">
         <x:v>TR2018-11</x:v>
       </x:c>
@@ -12164,8 +14024,17 @@
       <x:c r="L184" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="185" ht="42" customHeight="1">
+      <x:c r="M184" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N184" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O184" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="44" customHeight="1">
       <x:c r="A185" s="111" t="str">
         <x:v>TR2018-13</x:v>
       </x:c>
@@ -12204,8 +14073,17 @@
       <x:c r="L185" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="186" ht="42" customHeight="1">
+      <x:c r="M185" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N185" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O185" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="44" customHeight="1">
       <x:c r="A186" s="111" t="str">
         <x:v>TR2018-12</x:v>
       </x:c>
@@ -12244,8 +14122,17 @@
       <x:c r="L186" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="187" ht="42" customHeight="1">
+      <x:c r="M186" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N186" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O186" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="44" customHeight="1">
       <x:c r="A187" s="111" t="str">
         <x:v>TR2018-10</x:v>
       </x:c>
@@ -12284,8 +14171,17 @@
       <x:c r="L187" s="111" t="str">
         <x:v>S222;S223;S224;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="188" ht="42" customHeight="1">
+      <x:c r="M187" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N187" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O187" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="44" customHeight="1">
       <x:c r="A188" s="111" t="str">
         <x:v>TR2017-08</x:v>
       </x:c>
@@ -12324,8 +14220,17 @@
       <x:c r="L188" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="189" ht="42" customHeight="1">
+      <x:c r="M188" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N188" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O188" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="44" customHeight="1">
       <x:c r="A189" s="111" t="str">
         <x:v>TR2017-01</x:v>
       </x:c>
@@ -12364,8 +14269,17 @@
       <x:c r="L189" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="190" ht="42" customHeight="1">
+      <x:c r="M189" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N189" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O189" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="44" customHeight="1">
       <x:c r="A190" s="111" t="str">
         <x:v>TR2017-03</x:v>
       </x:c>
@@ -12404,8 +14318,17 @@
       <x:c r="L190" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="191" ht="42" customHeight="1">
+      <x:c r="M190" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N190" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O190" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="44" customHeight="1">
       <x:c r="A191" s="111" t="str">
         <x:v>TR2017-10</x:v>
       </x:c>
@@ -12444,8 +14367,17 @@
       <x:c r="L191" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="192" ht="42" customHeight="1">
+      <x:c r="M191" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N191" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O191" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="44" customHeight="1">
       <x:c r="A192" s="111" t="str">
         <x:v>TR2017-09</x:v>
       </x:c>
@@ -12484,8 +14416,17 @@
       <x:c r="L192" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="193" ht="42" customHeight="1">
+      <x:c r="M192" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N192" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O192" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="44" customHeight="1">
       <x:c r="A193" s="111" t="str">
         <x:v>TR2017-02</x:v>
       </x:c>
@@ -12524,8 +14465,17 @@
       <x:c r="L193" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="194" ht="42" customHeight="1">
+      <x:c r="M193" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N193" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O193" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="44" customHeight="1">
       <x:c r="A194" s="111" t="str">
         <x:v>TR2017-11</x:v>
       </x:c>
@@ -12564,8 +14514,17 @@
       <x:c r="L194" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="195" ht="42" customHeight="1">
+      <x:c r="M194" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N194" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O194" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="44" customHeight="1">
       <x:c r="A195" s="111" t="str">
         <x:v>TR2017-13</x:v>
       </x:c>
@@ -12604,8 +14563,17 @@
       <x:c r="L195" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="196" ht="42" customHeight="1">
+      <x:c r="M195" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N195" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O195" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="44" customHeight="1">
       <x:c r="A196" s="111" t="str">
         <x:v>TR2017-07</x:v>
       </x:c>
@@ -12644,8 +14612,17 @@
       <x:c r="L196" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="197" ht="42" customHeight="1">
+      <x:c r="M196" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N196" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O196" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="44" customHeight="1">
       <x:c r="A197" s="111" t="str">
         <x:v>TR2017-06</x:v>
       </x:c>
@@ -12684,8 +14661,17 @@
       <x:c r="L197" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="198" ht="42" customHeight="1">
+      <x:c r="M197" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N197" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O197" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="44" customHeight="1">
       <x:c r="A198" s="111" t="str">
         <x:v>TR2017-12</x:v>
       </x:c>
@@ -12724,8 +14710,17 @@
       <x:c r="L198" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="199" ht="42" customHeight="1">
+      <x:c r="M198" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N198" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O198" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="44" customHeight="1">
       <x:c r="A199" s="111" t="str">
         <x:v>TR2017-04</x:v>
       </x:c>
@@ -12764,8 +14759,17 @@
       <x:c r="L199" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="200" ht="42" customHeight="1">
+      <x:c r="M199" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N199" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O199" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="44" customHeight="1">
       <x:c r="A200" s="111" t="str">
         <x:v>TR2017-05</x:v>
       </x:c>
@@ -12804,8 +14808,17 @@
       <x:c r="L200" s="111" t="str">
         <x:v>S219;S220;S221;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="201" ht="42" customHeight="1">
+      <x:c r="M200" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N200" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O200" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="44" customHeight="1">
       <x:c r="A201" s="111" t="str">
         <x:v>TR2016-09</x:v>
       </x:c>
@@ -12844,8 +14857,17 @@
       <x:c r="L201" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="202" ht="42" customHeight="1">
+      <x:c r="M201" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N201" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O201" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="44" customHeight="1">
       <x:c r="A202" s="111" t="str">
         <x:v>TR2016-10</x:v>
       </x:c>
@@ -12884,8 +14906,17 @@
       <x:c r="L202" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="203" ht="42" customHeight="1">
+      <x:c r="M202" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N202" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O202" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="44" customHeight="1">
       <x:c r="A203" s="111" t="str">
         <x:v>EV0023</x:v>
       </x:c>
@@ -12924,8 +14955,17 @@
       <x:c r="L203" s="111" t="str">
         <x:v>S63</x:v>
       </x:c>
-    </x:row>
-    <x:row r="204" ht="42" customHeight="1">
+      <x:c r="M203" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N203" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O203" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="44" customHeight="1">
       <x:c r="A204" s="111" t="str">
         <x:v>TR2016-13</x:v>
       </x:c>
@@ -12964,8 +15004,17 @@
       <x:c r="L204" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="205" ht="42" customHeight="1">
+      <x:c r="M204" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N204" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O204" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="44" customHeight="1">
       <x:c r="A205" s="111" t="str">
         <x:v>TR2016-02</x:v>
       </x:c>
@@ -13004,8 +15053,17 @@
       <x:c r="L205" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="206" ht="42" customHeight="1">
+      <x:c r="M205" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N205" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O205" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="44" customHeight="1">
       <x:c r="A206" s="111" t="str">
         <x:v>TR2016-01</x:v>
       </x:c>
@@ -13044,8 +15102,17 @@
       <x:c r="L206" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="207" ht="42" customHeight="1">
+      <x:c r="M206" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N206" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O206" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="44" customHeight="1">
       <x:c r="A207" s="111" t="str">
         <x:v>EV0022</x:v>
       </x:c>
@@ -13084,8 +15151,17 @@
       <x:c r="L207" s="111" t="str">
         <x:v>S145</x:v>
       </x:c>
-    </x:row>
-    <x:row r="208" ht="42" customHeight="1">
+      <x:c r="M207" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N207" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O207" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="44" customHeight="1">
       <x:c r="A208" s="111" t="str">
         <x:v>TR2016-03</x:v>
       </x:c>
@@ -13124,8 +15200,17 @@
       <x:c r="L208" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="209" ht="42" customHeight="1">
+      <x:c r="M208" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N208" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O208" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="44" customHeight="1">
       <x:c r="A209" s="111" t="str">
         <x:v>TR2016-08</x:v>
       </x:c>
@@ -13164,8 +15249,17 @@
       <x:c r="L209" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="210" ht="42" customHeight="1">
+      <x:c r="M209" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N209" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O209" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="44" customHeight="1">
       <x:c r="A210" s="111" t="str">
         <x:v>TR2016-06</x:v>
       </x:c>
@@ -13204,8 +15298,17 @@
       <x:c r="L210" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="211" ht="42" customHeight="1">
+      <x:c r="M210" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N210" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O210" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="44" customHeight="1">
       <x:c r="A211" s="111" t="str">
         <x:v>TR2016-07</x:v>
       </x:c>
@@ -13244,8 +15347,17 @@
       <x:c r="L211" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="212" ht="42" customHeight="1">
+      <x:c r="M211" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N211" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O211" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="44" customHeight="1">
       <x:c r="A212" s="111" t="str">
         <x:v>TR2016-05</x:v>
       </x:c>
@@ -13284,8 +15396,17 @@
       <x:c r="L212" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="213" ht="42" customHeight="1">
+      <x:c r="M212" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N212" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O212" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="44" customHeight="1">
       <x:c r="A213" s="111" t="str">
         <x:v>TR2016-04</x:v>
       </x:c>
@@ -13324,8 +15445,17 @@
       <x:c r="L213" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="214" ht="42" customHeight="1">
+      <x:c r="M213" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N213" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O213" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="44" customHeight="1">
       <x:c r="A214" s="111" t="str">
         <x:v>TR2016-12</x:v>
       </x:c>
@@ -13364,8 +15494,17 @@
       <x:c r="L214" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="215" ht="42" customHeight="1">
+      <x:c r="M214" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N214" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O214" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="44" customHeight="1">
       <x:c r="A215" s="111" t="str">
         <x:v>TR2016-11</x:v>
       </x:c>
@@ -13404,8 +15543,17 @@
       <x:c r="L215" s="111" t="str">
         <x:v>S217;S218;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="216" ht="42" customHeight="1">
+      <x:c r="M215" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N215" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O215" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="44" customHeight="1">
       <x:c r="A216" s="111" t="str">
         <x:v>EV0021</x:v>
       </x:c>
@@ -13444,8 +15592,17 @@
       <x:c r="L216" s="111" t="str">
         <x:v>S162;S163</x:v>
       </x:c>
-    </x:row>
-    <x:row r="217" ht="42" customHeight="1">
+      <x:c r="M216" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N216" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O216" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="44" customHeight="1">
       <x:c r="A217" s="111" t="str">
         <x:v>TR2015-09</x:v>
       </x:c>
@@ -13484,8 +15641,17 @@
       <x:c r="L217" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="218" ht="42" customHeight="1">
+      <x:c r="M217" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N217" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O217" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="44" customHeight="1">
       <x:c r="A218" s="111" t="str">
         <x:v>TR2015-12</x:v>
       </x:c>
@@ -13524,8 +15690,17 @@
       <x:c r="L218" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="219" ht="42" customHeight="1">
+      <x:c r="M218" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N218" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O218" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="44" customHeight="1">
       <x:c r="A219" s="111" t="str">
         <x:v>TR2015-04</x:v>
       </x:c>
@@ -13564,8 +15739,17 @@
       <x:c r="L219" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="220" ht="42" customHeight="1">
+      <x:c r="M219" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N219" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O219" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="44" customHeight="1">
       <x:c r="A220" s="111" t="str">
         <x:v>TR2015-08</x:v>
       </x:c>
@@ -13604,8 +15788,17 @@
       <x:c r="L220" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="221" ht="42" customHeight="1">
+      <x:c r="M220" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N220" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O220" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="44" customHeight="1">
       <x:c r="A221" s="111" t="str">
         <x:v>TR2015-07</x:v>
       </x:c>
@@ -13644,8 +15837,17 @@
       <x:c r="L221" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="222" ht="42" customHeight="1">
+      <x:c r="M221" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N221" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O221" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="44" customHeight="1">
       <x:c r="A222" s="111" t="str">
         <x:v>TR2015-06</x:v>
       </x:c>
@@ -13684,8 +15886,17 @@
       <x:c r="L222" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="223" ht="42" customHeight="1">
+      <x:c r="M222" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N222" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O222" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="44" customHeight="1">
       <x:c r="A223" s="111" t="str">
         <x:v>TR2015-05</x:v>
       </x:c>
@@ -13724,8 +15935,17 @@
       <x:c r="L223" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="224" ht="42" customHeight="1">
+      <x:c r="M223" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N223" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O223" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="44" customHeight="1">
       <x:c r="A224" s="111" t="str">
         <x:v>TR2015-01</x:v>
       </x:c>
@@ -13764,8 +15984,17 @@
       <x:c r="L224" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="225" ht="42" customHeight="1">
+      <x:c r="M224" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N224" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O224" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="44" customHeight="1">
       <x:c r="A225" s="111" t="str">
         <x:v>TR2015-02</x:v>
       </x:c>
@@ -13804,8 +16033,17 @@
       <x:c r="L225" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="226" ht="42" customHeight="1">
+      <x:c r="M225" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N225" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O225" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="44" customHeight="1">
       <x:c r="A226" s="111" t="str">
         <x:v>TR2015-03</x:v>
       </x:c>
@@ -13844,8 +16082,17 @@
       <x:c r="L226" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="227" ht="42" customHeight="1">
+      <x:c r="M226" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N226" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O226" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="44" customHeight="1">
       <x:c r="A227" s="111" t="str">
         <x:v>TR2015-10</x:v>
       </x:c>
@@ -13884,8 +16131,17 @@
       <x:c r="L227" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="228" ht="42" customHeight="1">
+      <x:c r="M227" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N227" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O227" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="44" customHeight="1">
       <x:c r="A228" s="111" t="str">
         <x:v>TR2015-11</x:v>
       </x:c>
@@ -13924,8 +16180,17 @@
       <x:c r="L228" s="111" t="str">
         <x:v>S215;S216;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="229" ht="42" customHeight="1">
+      <x:c r="M228" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N228" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O228" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="44" customHeight="1">
       <x:c r="A229" s="111" t="str">
         <x:v>EV0017</x:v>
       </x:c>
@@ -13964,8 +16229,17 @@
       <x:c r="L229" s="111" t="str">
         <x:v>S105</x:v>
       </x:c>
-    </x:row>
-    <x:row r="230" ht="42" customHeight="1">
+      <x:c r="M229" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N229" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O229" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="44" customHeight="1">
       <x:c r="A230" s="111" t="str">
         <x:v>EV0018</x:v>
       </x:c>
@@ -14004,8 +16278,17 @@
       <x:c r="L230" s="111" t="str">
         <x:v>S146;S147</x:v>
       </x:c>
-    </x:row>
-    <x:row r="231" ht="42" customHeight="1">
+      <x:c r="M230" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N230" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O230" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="44" customHeight="1">
       <x:c r="A231" s="111" t="str">
         <x:v>TR2014-02</x:v>
       </x:c>
@@ -14044,8 +16327,17 @@
       <x:c r="L231" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="232" ht="42" customHeight="1">
+      <x:c r="M231" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N231" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O231" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="44" customHeight="1">
       <x:c r="A232" s="111" t="str">
         <x:v>EV0014</x:v>
       </x:c>
@@ -14084,8 +16376,17 @@
       <x:c r="L232" s="111" t="str">
         <x:v>S53</x:v>
       </x:c>
-    </x:row>
-    <x:row r="233" ht="42" customHeight="1">
+      <x:c r="M232" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N232" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O232" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="44" customHeight="1">
       <x:c r="A233" s="111" t="str">
         <x:v>TR2014-11</x:v>
       </x:c>
@@ -14124,8 +16425,17 @@
       <x:c r="L233" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="234" ht="42" customHeight="1">
+      <x:c r="M233" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N233" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O233" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="44" customHeight="1">
       <x:c r="A234" s="111" t="str">
         <x:v>EV0016</x:v>
       </x:c>
@@ -14164,8 +16474,17 @@
       <x:c r="L234" s="111" t="str">
         <x:v>S62</x:v>
       </x:c>
-    </x:row>
-    <x:row r="235" ht="42" customHeight="1">
+      <x:c r="M234" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N234" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O234" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="44" customHeight="1">
       <x:c r="A235" s="111" t="str">
         <x:v>TR2014-04</x:v>
       </x:c>
@@ -14204,8 +16523,17 @@
       <x:c r="L235" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="236" ht="42" customHeight="1">
+      <x:c r="M235" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N235" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O235" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="44" customHeight="1">
       <x:c r="A236" s="111" t="str">
         <x:v>TR2014-07</x:v>
       </x:c>
@@ -14244,8 +16572,17 @@
       <x:c r="L236" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="237" ht="42" customHeight="1">
+      <x:c r="M236" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N236" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O236" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="44" customHeight="1">
       <x:c r="A237" s="111" t="str">
         <x:v>TR2014-01</x:v>
       </x:c>
@@ -14284,8 +16621,17 @@
       <x:c r="L237" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="238" ht="42" customHeight="1">
+      <x:c r="M237" s="822" t="str">
+        <x:v>아동·10대/가족 관심 가능성</x:v>
+      </x:c>
+      <x:c r="N237" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O237" s="822" t="str">
+        <x:v>실측 없음·아동·캐릭터·가족 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="44" customHeight="1">
       <x:c r="A238" s="111" t="str">
         <x:v>TR2014-08</x:v>
       </x:c>
@@ -14324,8 +16670,17 @@
       <x:c r="L238" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="239" ht="42" customHeight="1">
+      <x:c r="M238" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N238" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O238" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="44" customHeight="1">
       <x:c r="A239" s="111" t="str">
         <x:v>TR2014-05</x:v>
       </x:c>
@@ -14364,8 +16719,17 @@
       <x:c r="L239" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="240" ht="42" customHeight="1">
+      <x:c r="M239" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N239" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O239" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="44" customHeight="1">
       <x:c r="A240" s="111" t="str">
         <x:v>TR2014-03</x:v>
       </x:c>
@@ -14404,8 +16768,17 @@
       <x:c r="L240" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="241" ht="42" customHeight="1">
+      <x:c r="M240" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N240" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O240" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="44" customHeight="1">
       <x:c r="A241" s="111" t="str">
         <x:v>TR2014-09</x:v>
       </x:c>
@@ -14444,8 +16817,17 @@
       <x:c r="L241" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="242" ht="42" customHeight="1">
+      <x:c r="M241" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N241" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O241" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="44" customHeight="1">
       <x:c r="A242" s="111" t="str">
         <x:v>EV0015</x:v>
       </x:c>
@@ -14484,8 +16866,17 @@
       <x:c r="L242" s="111" t="str">
         <x:v>S157</x:v>
       </x:c>
-    </x:row>
-    <x:row r="243" ht="42" customHeight="1">
+      <x:c r="M242" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N242" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O242" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="44" customHeight="1">
       <x:c r="A243" s="111" t="str">
         <x:v>TR2014-06</x:v>
       </x:c>
@@ -14524,8 +16915,17 @@
       <x:c r="L243" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="244" ht="42" customHeight="1">
+      <x:c r="M243" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N243" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O243" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="44" customHeight="1">
       <x:c r="A244" s="111" t="str">
         <x:v>TR2014-10</x:v>
       </x:c>
@@ -14564,8 +16964,17 @@
       <x:c r="L244" s="111" t="str">
         <x:v>S213;S214;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="245" ht="42" customHeight="1">
+      <x:c r="M244" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N244" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O244" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="44" customHeight="1">
       <x:c r="A245" s="111" t="str">
         <x:v>TR2013-08</x:v>
       </x:c>
@@ -14604,8 +17013,17 @@
       <x:c r="L245" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="246" ht="42" customHeight="1">
+      <x:c r="M245" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N245" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O245" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="44" customHeight="1">
       <x:c r="A246" s="111" t="str">
         <x:v>TR2013-07</x:v>
       </x:c>
@@ -14644,8 +17062,17 @@
       <x:c r="L246" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="247" ht="42" customHeight="1">
+      <x:c r="M246" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N246" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O246" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="44" customHeight="1">
       <x:c r="A247" s="111" t="str">
         <x:v>TR2013-06</x:v>
       </x:c>
@@ -14684,8 +17111,17 @@
       <x:c r="L247" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="248" ht="42" customHeight="1">
+      <x:c r="M247" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N247" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O247" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="44" customHeight="1">
       <x:c r="A248" s="111" t="str">
         <x:v>TR2013-09</x:v>
       </x:c>
@@ -14724,8 +17160,17 @@
       <x:c r="L248" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="249" ht="42" customHeight="1">
+      <x:c r="M248" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N248" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O248" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="44" customHeight="1">
       <x:c r="A249" s="111" t="str">
         <x:v>TR2013-05</x:v>
       </x:c>
@@ -14764,8 +17209,17 @@
       <x:c r="L249" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="250" ht="42" customHeight="1">
+      <x:c r="M249" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N249" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O249" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="44" customHeight="1">
       <x:c r="A250" s="111" t="str">
         <x:v>TR2013-10</x:v>
       </x:c>
@@ -14804,8 +17258,17 @@
       <x:c r="L250" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="251" ht="42" customHeight="1">
+      <x:c r="M250" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N250" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O250" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="44" customHeight="1">
       <x:c r="A251" s="111" t="str">
         <x:v>TR2013-04</x:v>
       </x:c>
@@ -14844,8 +17307,17 @@
       <x:c r="L251" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="252" ht="42" customHeight="1">
+      <x:c r="M251" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N251" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O251" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="44" customHeight="1">
       <x:c r="A252" s="111" t="str">
         <x:v>TR2013-01</x:v>
       </x:c>
@@ -14884,8 +17356,17 @@
       <x:c r="L252" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="253" ht="42" customHeight="1">
+      <x:c r="M252" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N252" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O252" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="44" customHeight="1">
       <x:c r="A253" s="111" t="str">
         <x:v>TR2013-03</x:v>
       </x:c>
@@ -14924,8 +17405,17 @@
       <x:c r="L253" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="254" ht="42" customHeight="1">
+      <x:c r="M253" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N253" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O253" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="44" customHeight="1">
       <x:c r="A254" s="111" t="str">
         <x:v>TR2013-02</x:v>
       </x:c>
@@ -14964,8 +17454,17 @@
       <x:c r="L254" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="255" ht="42" customHeight="1">
+      <x:c r="M254" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N254" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O254" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="44" customHeight="1">
       <x:c r="A255" s="111" t="str">
         <x:v>TR2013-11</x:v>
       </x:c>
@@ -15004,8 +17503,17 @@
       <x:c r="L255" s="111" t="str">
         <x:v>S211;S212;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="256" ht="42" customHeight="1">
+      <x:c r="M255" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N255" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O255" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="44" customHeight="1">
       <x:c r="A256" s="111" t="str">
         <x:v>EV0013</x:v>
       </x:c>
@@ -15044,8 +17552,17 @@
       <x:c r="L256" s="111" t="str">
         <x:v>S104</x:v>
       </x:c>
-    </x:row>
-    <x:row r="257" ht="42" customHeight="1">
+      <x:c r="M256" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N256" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O256" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="44" customHeight="1">
       <x:c r="A257" s="111" t="str">
         <x:v>TR2012-09</x:v>
       </x:c>
@@ -15084,8 +17601,17 @@
       <x:c r="L257" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="258" ht="42" customHeight="1">
+      <x:c r="M257" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N257" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O257" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="44" customHeight="1">
       <x:c r="A258" s="111" t="str">
         <x:v>TR2012-05</x:v>
       </x:c>
@@ -15124,8 +17650,17 @@
       <x:c r="L258" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="259" ht="42" customHeight="1">
+      <x:c r="M258" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N258" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O258" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="44" customHeight="1">
       <x:c r="A259" s="111" t="str">
         <x:v>EV0011</x:v>
       </x:c>
@@ -15164,8 +17699,17 @@
       <x:c r="L259" s="111" t="str">
         <x:v>S31;S32</x:v>
       </x:c>
-    </x:row>
-    <x:row r="260" ht="42" customHeight="1">
+      <x:c r="M259" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N259" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O259" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="44" customHeight="1">
       <x:c r="A260" s="111" t="str">
         <x:v>TR2012-08</x:v>
       </x:c>
@@ -15204,8 +17748,17 @@
       <x:c r="L260" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="261" ht="42" customHeight="1">
+      <x:c r="M260" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N260" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O260" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="44" customHeight="1">
       <x:c r="A261" s="111" t="str">
         <x:v>TR2012-10</x:v>
       </x:c>
@@ -15244,8 +17797,17 @@
       <x:c r="L261" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="262" ht="42" customHeight="1">
+      <x:c r="M261" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N261" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O261" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="44" customHeight="1">
       <x:c r="A262" s="111" t="str">
         <x:v>TR2012-02</x:v>
       </x:c>
@@ -15284,8 +17846,17 @@
       <x:c r="L262" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="263" ht="42" customHeight="1">
+      <x:c r="M262" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N262" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O262" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="44" customHeight="1">
       <x:c r="A263" s="111" t="str">
         <x:v>TR2012-07</x:v>
       </x:c>
@@ -15324,8 +17895,17 @@
       <x:c r="L263" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="264" ht="42" customHeight="1">
+      <x:c r="M263" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N263" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O263" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="44" customHeight="1">
       <x:c r="A264" s="111" t="str">
         <x:v>TR2012-01</x:v>
       </x:c>
@@ -15364,8 +17944,17 @@
       <x:c r="L264" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="265" ht="42" customHeight="1">
+      <x:c r="M264" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N264" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O264" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="44" customHeight="1">
       <x:c r="A265" s="111" t="str">
         <x:v>TR2012-03</x:v>
       </x:c>
@@ -15404,8 +17993,17 @@
       <x:c r="L265" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="266" ht="42" customHeight="1">
+      <x:c r="M265" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N265" s="822" t="str">
+        <x:v>남성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O265" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="44" customHeight="1">
       <x:c r="A266" s="111" t="str">
         <x:v>TR2012-06</x:v>
       </x:c>
@@ -15444,8 +18042,17 @@
       <x:c r="L266" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="267" ht="42" customHeight="1">
+      <x:c r="M266" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N266" s="822" t="str">
+        <x:v>여성 관심 가능성(추정)</x:v>
+      </x:c>
+      <x:c r="O266" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="44" customHeight="1">
       <x:c r="A267" s="111" t="str">
         <x:v>TR2012-04</x:v>
       </x:c>
@@ -15484,8 +18091,17 @@
       <x:c r="L267" s="111" t="str">
         <x:v>S209;S210;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="268" ht="42" customHeight="1">
+      <x:c r="M267" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N267" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O267" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="44" customHeight="1">
       <x:c r="A268" s="111" t="str">
         <x:v>TR2011-08</x:v>
       </x:c>
@@ -15524,8 +18140,17 @@
       <x:c r="L268" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="269" ht="42" customHeight="1">
+      <x:c r="M268" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N268" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O268" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="44" customHeight="1">
       <x:c r="A269" s="111" t="str">
         <x:v>TR2011-07</x:v>
       </x:c>
@@ -15564,8 +18189,17 @@
       <x:c r="L269" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="270" ht="42" customHeight="1">
+      <x:c r="M269" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N269" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O269" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="44" customHeight="1">
       <x:c r="A270" s="111" t="str">
         <x:v>TR2011-03</x:v>
       </x:c>
@@ -15604,8 +18238,17 @@
       <x:c r="L270" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="271" ht="42" customHeight="1">
+      <x:c r="M270" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N270" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O270" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="44" customHeight="1">
       <x:c r="A271" s="111" t="str">
         <x:v>TR2011-02</x:v>
       </x:c>
@@ -15644,8 +18287,17 @@
       <x:c r="L271" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="272" ht="42" customHeight="1">
+      <x:c r="M271" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N271" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O271" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="44" customHeight="1">
       <x:c r="A272" s="111" t="str">
         <x:v>TR2011-01</x:v>
       </x:c>
@@ -15684,8 +18336,17 @@
       <x:c r="L272" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="273" ht="42" customHeight="1">
+      <x:c r="M272" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N272" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O272" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="44" customHeight="1">
       <x:c r="A273" s="111" t="str">
         <x:v>TR2011-09</x:v>
       </x:c>
@@ -15724,8 +18385,17 @@
       <x:c r="L273" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="274" ht="42" customHeight="1">
+      <x:c r="M273" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N273" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O273" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="44" customHeight="1">
       <x:c r="A274" s="111" t="str">
         <x:v>TR2011-05</x:v>
       </x:c>
@@ -15764,8 +18434,17 @@
       <x:c r="L274" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="275" ht="42" customHeight="1">
+      <x:c r="M274" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N274" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O274" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="44" customHeight="1">
       <x:c r="A275" s="111" t="str">
         <x:v>TR2011-04</x:v>
       </x:c>
@@ -15804,8 +18483,17 @@
       <x:c r="L275" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="276" ht="42" customHeight="1">
+      <x:c r="M275" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N275" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O275" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="44" customHeight="1">
       <x:c r="A276" s="111" t="str">
         <x:v>TR2011-06</x:v>
       </x:c>
@@ -15844,8 +18532,17 @@
       <x:c r="L276" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="277" ht="42" customHeight="1">
+      <x:c r="M276" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N276" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O276" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="44" customHeight="1">
       <x:c r="A277" s="111" t="str">
         <x:v>TR2011-10</x:v>
       </x:c>
@@ -15884,8 +18581,17 @@
       <x:c r="L277" s="111" t="str">
         <x:v>S207;S208;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="278" ht="42" customHeight="1">
+      <x:c r="M277" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N277" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O277" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="44" customHeight="1">
       <x:c r="A278" s="111" t="str">
         <x:v>EV0010</x:v>
       </x:c>
@@ -15924,8 +18630,17 @@
       <x:c r="L278" s="111" t="str">
         <x:v>S156</x:v>
       </x:c>
-    </x:row>
-    <x:row r="279" ht="42" customHeight="1">
+      <x:c r="M278" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N278" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O278" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="44" customHeight="1">
       <x:c r="A279" s="111" t="str">
         <x:v>TR2010-02</x:v>
       </x:c>
@@ -15964,8 +18679,17 @@
       <x:c r="L279" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="280" ht="42" customHeight="1">
+      <x:c r="M279" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N279" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O279" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="44" customHeight="1">
       <x:c r="A280" s="111" t="str">
         <x:v>EV0006</x:v>
       </x:c>
@@ -16004,8 +18728,17 @@
       <x:c r="L280" s="111" t="str">
         <x:v>S103</x:v>
       </x:c>
-    </x:row>
-    <x:row r="281" ht="42" customHeight="1">
+      <x:c r="M280" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N280" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O280" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="44" customHeight="1">
       <x:c r="A281" s="111" t="str">
         <x:v>TR2010-10</x:v>
       </x:c>
@@ -16044,8 +18777,17 @@
       <x:c r="L281" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="282" ht="42" customHeight="1">
+      <x:c r="M281" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N281" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O281" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="44" customHeight="1">
       <x:c r="A282" s="111" t="str">
         <x:v>EV0007</x:v>
       </x:c>
@@ -16084,8 +18826,17 @@
       <x:c r="L282" s="111" t="str">
         <x:v>S102</x:v>
       </x:c>
-    </x:row>
-    <x:row r="283" ht="42" customHeight="1">
+      <x:c r="M282" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N282" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O282" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="44" customHeight="1">
       <x:c r="A283" s="111" t="str">
         <x:v>EV0008</x:v>
       </x:c>
@@ -16124,8 +18875,17 @@
       <x:c r="L283" s="111" t="str">
         <x:v>S96</x:v>
       </x:c>
-    </x:row>
-    <x:row r="284" ht="42" customHeight="1">
+      <x:c r="M283" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N283" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O283" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="44" customHeight="1">
       <x:c r="A284" s="111" t="str">
         <x:v>TR2010-03</x:v>
       </x:c>
@@ -16164,8 +18924,17 @@
       <x:c r="L284" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="285" ht="42" customHeight="1">
+      <x:c r="M284" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N284" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O284" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="44" customHeight="1">
       <x:c r="A285" s="111" t="str">
         <x:v>TR2010-01</x:v>
       </x:c>
@@ -16204,8 +18973,17 @@
       <x:c r="L285" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="286" ht="42" customHeight="1">
+      <x:c r="M285" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N285" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O285" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="44" customHeight="1">
       <x:c r="A286" s="111" t="str">
         <x:v>TR2010-05</x:v>
       </x:c>
@@ -16244,8 +19022,17 @@
       <x:c r="L286" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="287" ht="42" customHeight="1">
+      <x:c r="M286" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N286" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O286" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="44" customHeight="1">
       <x:c r="A287" s="111" t="str">
         <x:v>TR2010-07</x:v>
       </x:c>
@@ -16284,8 +19071,17 @@
       <x:c r="L287" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="288" ht="42" customHeight="1">
+      <x:c r="M287" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N287" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O287" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="44" customHeight="1">
       <x:c r="A288" s="111" t="str">
         <x:v>TR2010-04</x:v>
       </x:c>
@@ -16324,8 +19120,17 @@
       <x:c r="L288" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="289" ht="42" customHeight="1">
+      <x:c r="M288" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N288" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O288" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="44" customHeight="1">
       <x:c r="A289" s="111" t="str">
         <x:v>EV0009</x:v>
       </x:c>
@@ -16364,8 +19169,17 @@
       <x:c r="L289" s="111" t="str">
         <x:v>S80;S96</x:v>
       </x:c>
-    </x:row>
-    <x:row r="290" ht="42" customHeight="1">
+      <x:c r="M289" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N289" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O289" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="44" customHeight="1">
       <x:c r="A290" s="111" t="str">
         <x:v>TR2010-08</x:v>
       </x:c>
@@ -16404,8 +19218,17 @@
       <x:c r="L290" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="291" ht="42" customHeight="1">
+      <x:c r="M290" s="822" t="str">
+        <x:v>10·30대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N290" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O290" s="822" t="str">
+        <x:v>실측 없음·패션·뷰티·인증 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="44" customHeight="1">
       <x:c r="A291" s="111" t="str">
         <x:v>TR2010-06</x:v>
       </x:c>
@@ -16444,8 +19267,17 @@
       <x:c r="L291" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="292" ht="42" customHeight="1">
+      <x:c r="M291" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N291" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O291" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="44" customHeight="1">
       <x:c r="A292" s="111" t="str">
         <x:v>TR2010-09</x:v>
       </x:c>
@@ -16484,8 +19316,17 @@
       <x:c r="L292" s="111" t="str">
         <x:v>S204;S205;S206;S237</x:v>
       </x:c>
-    </x:row>
-    <x:row r="293" ht="42" customHeight="1">
+      <x:c r="M292" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N292" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O292" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="44" customHeight="1">
       <x:c r="A293" s="111" t="str">
         <x:v>TR2009-07</x:v>
       </x:c>
@@ -16524,8 +19365,17 @@
       <x:c r="L293" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="294" ht="42" customHeight="1">
+      <x:c r="M293" s="822" t="str">
+        <x:v>20·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N293" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O293" s="822" t="str">
+        <x:v>실측 없음·일상 소비·검색 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="44" customHeight="1">
       <x:c r="A294" s="111" t="str">
         <x:v>TR2009-01</x:v>
       </x:c>
@@ -16564,8 +19414,17 @@
       <x:c r="L294" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="295" ht="42" customHeight="1">
+      <x:c r="M294" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N294" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O294" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="44" customHeight="1">
       <x:c r="A295" s="111" t="str">
         <x:v>TR2009-09</x:v>
       </x:c>
@@ -16604,8 +19463,17 @@
       <x:c r="L295" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="296" ht="42" customHeight="1">
+      <x:c r="M295" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N295" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O295" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="44" customHeight="1">
       <x:c r="A296" s="111" t="str">
         <x:v>TR2009-03</x:v>
       </x:c>
@@ -16644,8 +19512,17 @@
       <x:c r="L296" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="297" ht="42" customHeight="1">
+      <x:c r="M296" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N296" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O296" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="44" customHeight="1">
       <x:c r="A297" s="111" t="str">
         <x:v>TR2009-02</x:v>
       </x:c>
@@ -16684,8 +19561,17 @@
       <x:c r="L297" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="298" ht="42" customHeight="1">
+      <x:c r="M297" s="822" t="str">
+        <x:v>10·20대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N297" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O297" s="822" t="str">
+        <x:v>실측 없음·게임·팬덤·숏폼 확산 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="44" customHeight="1">
       <x:c r="A298" s="111" t="str">
         <x:v>TR2009-08</x:v>
       </x:c>
@@ -16724,8 +19610,17 @@
       <x:c r="L298" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="299" ht="42" customHeight="1">
+      <x:c r="M298" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N298" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O298" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="44" customHeight="1">
       <x:c r="A299" s="111" t="str">
         <x:v>TR2009-06</x:v>
       </x:c>
@@ -16764,8 +19659,17 @@
       <x:c r="L299" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="300" ht="42" customHeight="1">
+      <x:c r="M299" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N299" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O299" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="44" customHeight="1">
       <x:c r="A300" s="111" t="str">
         <x:v>TR2009-05</x:v>
       </x:c>
@@ -16804,8 +19708,17 @@
       <x:c r="L300" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="301" ht="42" customHeight="1">
+      <x:c r="M300" s="822" t="str">
+        <x:v>10·40대 중심 가능성</x:v>
+      </x:c>
+      <x:c r="N300" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O300" s="822" t="str">
+        <x:v>실측 없음·온라인 콘텐츠·플랫폼 이용 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="44" customHeight="1">
       <x:c r="A301" s="111" t="str">
         <x:v>EV0004</x:v>
       </x:c>
@@ -16844,8 +19757,17 @@
       <x:c r="L301" s="111" t="str">
         <x:v>S101;S100</x:v>
       </x:c>
-    </x:row>
-    <x:row r="302" ht="42" customHeight="1">
+      <x:c r="M301" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N301" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O301" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="44" customHeight="1">
       <x:c r="A302" s="111" t="str">
         <x:v>TR2009-04</x:v>
       </x:c>
@@ -16884,8 +19806,17 @@
       <x:c r="L302" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
-    </x:row>
-    <x:row r="303" ht="42" customHeight="1">
+      <x:c r="M302" s="822" t="str">
+        <x:v>30대 이상·중장년 포함 가능성</x:v>
+      </x:c>
+      <x:c r="N302" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O302" s="822" t="str">
+        <x:v>실측 없음·건강·취미·복고 소비 맥락 기반 추정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="44" customHeight="1">
       <x:c r="A303" s="111" t="str">
         <x:v>TR2009-10</x:v>
       </x:c>
@@ -16924,11 +19855,21 @@
       <x:c r="L303" s="111" t="str">
         <x:v>S201;S202;S203</x:v>
       </x:c>
+      <x:c r="M303" s="822" t="str">
+        <x:v>전 연령·혼합 가능성</x:v>
+      </x:c>
+      <x:c r="N303" s="822" t="str">
+        <x:v>혼합·성별 차이 미확인</x:v>
+      </x:c>
+      <x:c r="O303" s="822" t="str">
+        <x:v>실측 없음·대중적 참여·사회 확산 맥락 기반 추정</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:L1"/>
-    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A1:O1"/>
+    <x:mergeCell ref="A2:O2"/>
+    <x:mergeCell ref="M3:O3"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="H6:H75">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="상승"/>
@@ -16941,7 +19882,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ed60b71aef04103"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b35ac89ba794880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29711,7 +32652,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e72239bf7a4332"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcfb1aff04954ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30208,6 +33149,174 @@
       <x:c r="G28" s="175"/>
       <x:c r="H28" s="175"/>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="823" t="str">
+        <x:v>연령·성별 추정값 사용 규칙 — 실측 통계와 구분</x:v>
+      </x:c>
+      <x:c r="B30" s="823"/>
+      <x:c r="C30" s="823"/>
+      <x:c r="D30" s="823"/>
+      <x:c r="E30" s="823"/>
+      <x:c r="F30" s="823"/>
+      <x:c r="G30" s="823"/>
+      <x:c r="H30" s="823"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="824" t="str">
+        <x:v>항목</x:v>
+      </x:c>
+      <x:c r="B31" s="824" t="str">
+        <x:v>판정 원칙</x:v>
+      </x:c>
+      <x:c r="C31" s="824" t="str">
+        <x:v>허용 표현</x:v>
+      </x:c>
+      <x:c r="D31" s="824" t="str">
+        <x:v>금지 표현</x:v>
+      </x:c>
+      <x:c r="E31" s="824" t="str">
+        <x:v>현재 근거</x:v>
+      </x:c>
+      <x:c r="F31" s="824" t="str">
+        <x:v>후속 검증</x:v>
+      </x:c>
+      <x:c r="G31" s="824" t="str">
+        <x:v>서비스 표기</x:v>
+      </x:c>
+      <x:c r="H31" s="824" t="str">
+        <x:v>주의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="A32" s="825" t="str">
+        <x:v>데이터 성격</x:v>
+      </x:c>
+      <x:c r="B32" s="815" t="str">
+        <x:v>사건명·소분류·확산 플랫폼에서 관심 가능성을 추정</x:v>
+      </x:c>
+      <x:c r="C32" s="815" t="str">
+        <x:v>‘중심 가능성’, ‘혼합’</x:v>
+      </x:c>
+      <x:c r="D32" s="815" t="str">
+        <x:v>실제 이용자 비율로 단정</x:v>
+      </x:c>
+      <x:c r="E32" s="815" t="str">
+        <x:v>실측 없음</x:v>
+      </x:c>
+      <x:c r="F32" s="815" t="str">
+        <x:v>플랫폼 분석·설문 확보</x:v>
+      </x:c>
+      <x:c r="G32" s="815" t="str">
+        <x:v>반드시 ‘추정’ 표시</x:v>
+      </x:c>
+      <x:c r="H32" s="815" t="str">
+        <x:v>투자 판단 근거 아님</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="825" t="str">
+        <x:v>연령대</x:v>
+      </x:c>
+      <x:c r="B33" s="815" t="str">
+        <x:v>아동/청년/중장년/전 연령 소비 맥락을 보수적으로 구분</x:v>
+      </x:c>
+      <x:c r="C33" s="815" t="str">
+        <x:v>아동·10대/가족, 10·20대, 10·30대, 10·40대, 20·40대, 중장년 포함, 전 연령</x:v>
+      </x:c>
+      <x:c r="D33" s="815" t="str">
+        <x:v>특정 연령만 관심</x:v>
+      </x:c>
+      <x:c r="E33" s="815" t="str">
+        <x:v>사건·플랫폼 맥락</x:v>
+      </x:c>
+      <x:c r="F33" s="815" t="str">
+        <x:v>검색·SNS 연령 통계로 교체</x:v>
+      </x:c>
+      <x:c r="G33" s="815" t="str">
+        <x:v>주요 관심 연령대(추정)</x:v>
+      </x:c>
+      <x:c r="H33" s="815" t="str">
+        <x:v>‘중심’은 배타적 의미가 아님</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="825" t="str">
+        <x:v>성별</x:v>
+      </x:c>
+      <x:c r="B34" s="815" t="str">
+        <x:v>기본값은 혼합·차이 미확인; 뷰티·게임 등 강한 맥락만 가능성 표기</x:v>
+      </x:c>
+      <x:c r="C34" s="815" t="str">
+        <x:v>혼합·차이 미확인, 여성/남성 관심 가능성</x:v>
+      </x:c>
+      <x:c r="D34" s="815" t="str">
+        <x:v>여성/남성이 실제 다수</x:v>
+      </x:c>
+      <x:c r="E34" s="815" t="str">
+        <x:v>사건·카테고리 맥락</x:v>
+      </x:c>
+      <x:c r="F34" s="815" t="str">
+        <x:v>성별 이용 통계로 교체</x:v>
+      </x:c>
+      <x:c r="G34" s="815" t="str">
+        <x:v>성별 관심 경향(추정)</x:v>
+      </x:c>
+      <x:c r="H34" s="815" t="str">
+        <x:v>고정관념으로 확대 해석 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="825" t="str">
+        <x:v>근거 수준</x:v>
+      </x:c>
+      <x:c r="B35" s="815" t="str">
+        <x:v>모든 행에 실측 여부와 추정 근거를 함께 표시</x:v>
+      </x:c>
+      <x:c r="C35" s="815" t="str">
+        <x:v>실측 없음·○○ 맥락 기반 추정</x:v>
+      </x:c>
+      <x:c r="D35" s="815" t="str">
+        <x:v>조사 통계, 실측 결과</x:v>
+      </x:c>
+      <x:c r="E35" s="815" t="str">
+        <x:v>298건 모두 추정</x:v>
+      </x:c>
+      <x:c r="F35" s="815" t="str">
+        <x:v>실측 확보 시 행별 갱신</x:v>
+      </x:c>
+      <x:c r="G35" s="815" t="str">
+        <x:v>인구통계 근거 수준</x:v>
+      </x:c>
+      <x:c r="H35" s="815" t="str">
+        <x:v>출처 없는 숫자 생성 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="825" t="str">
+        <x:v>활용 범위</x:v>
+      </x:c>
+      <x:c r="B36" s="815" t="str">
+        <x:v>서비스 기준을 설계하기 위한 조사 가설로만 사용</x:v>
+      </x:c>
+      <x:c r="C36" s="815" t="str">
+        <x:v>후속 인터뷰·정량조사 후보</x:v>
+      </x:c>
+      <x:c r="D36" s="815" t="str">
+        <x:v>타기팅 확정값</x:v>
+      </x:c>
+      <x:c r="E36" s="815" t="str">
+        <x:v>초기 탐색 단계</x:v>
+      </x:c>
+      <x:c r="F36" s="815" t="str">
+        <x:v>네이버 데이터랩·플랫폼 애널리틱스·패널조사</x:v>
+      </x:c>
+      <x:c r="G36" s="815" t="str">
+        <x:v>추정 배지 유지</x:v>
+      </x:c>
+      <x:c r="H36" s="815" t="str">
+        <x:v>개인 속성 추론에 사용 금지</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -30224,6 +33333,7 @@
     <x:mergeCell ref="B26:H26"/>
     <x:mergeCell ref="B27:H27"/>
     <x:mergeCell ref="B28:H28"/>
+    <x:mergeCell ref="A30:H30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
